--- a/dashboard_report.xlsx
+++ b/dashboard_report.xlsx
@@ -415,12 +415,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -454,16 +454,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -474,16 +474,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6"/>
@@ -583,43 +583,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Weekly Sales</t>
-        </is>
-      </c>
-    </row>
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Value</t>
+          <t>Weekly Sales</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -629,7 +629,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -639,7 +639,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -649,7 +649,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -659,7 +659,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -669,10 +669,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -687,11 +697,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
@@ -726,7 +736,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119449</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -786,7 +796,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119449</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -858,40 +868,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Weekly Sales</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>119449</v>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Value</t>
+          <t>Weekly Sales</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -901,7 +911,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -911,7 +921,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -921,7 +931,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -931,7 +941,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -941,11 +951,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>119449</v>
       </c>
     </row>
   </sheetData>
@@ -959,14 +979,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -984,7 +1004,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1028,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1047,39 +1067,2439 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ITEM001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wahoo Ceviche</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cold Appetizer</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7500.00</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Staff</t>
+          <t>ITEM002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lobster Thermidor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mains</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>19200.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>ITEM003</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Margherita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ITEM004</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JIM BEAM 1Lt.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BOURBON</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>76000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ITEM005</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JIM BEAM Per Shot</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BOURBON</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ITEM006</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JIM BEAM BLACK</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BOURBON</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>25000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ITEM007</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tuna Crudo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cold Appetizer</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ITEM008</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Estrella Galicia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Beers</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>750.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ITEM009</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Heineken</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Beers</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ITEM010</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>San Mig Apple</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Beers</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ITEM011</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MOET CHANDON BRUT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CHAMPAGNE / SPARKLING WINE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>31500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ITEM012</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HENESSY VS 750ml</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COGNAC / BRANDY</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>34000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ITEM013</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pinacolada</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Classic Cocktails</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ITEM014</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sex On The Beach</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Classic Cocktails</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ITEM015</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Green Tea</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Coffee &amp; Tea</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ITEM016</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mango Lemonade</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mocktails</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ITEM017</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SPELLBOUND PINOT NOIR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RED WINE</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>6000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ITEM018</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MAKERS MARK 750ML</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BOURBON</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>157500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ITEM019</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Coconut Mousse</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>21</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>6300.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ITEM020</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Split Bill Paid</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>33</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-298282.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ITEM021</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Americano</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Coffee &amp; Tea</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>640.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ITEM022</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cafe Latte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Coffee &amp; Tea</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ITEM023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Black Tea</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Coffee &amp; Tea</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>270.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ITEM024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Calamares</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Crispy Bites</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>4800.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ITEM025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mexisisig</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sizzlers</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>4950.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ITEM026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pulled Beef Sandwich</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sandwiches, Burgers &amp; Snacks</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>550.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ITEM027</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Caesar Salad Grande</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Salad &amp; Dips</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>6000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ITEM028</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chirashi Sashimi</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>5250.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ITEM029</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Marina Verde Lasagna</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>8040.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ITEM030</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Salmon</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fresh from the Sea</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>800.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ITEM031</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DOM PERIGNON BRUT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CHAMPAGNE / SPARKLING WINE</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>45000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ITEM032</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>VEUVE CLIQUOT BRUT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CHAMPAGNE / SPARKLING WINE</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>75000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ITEM033</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pizza Frita Ala Nutella Smores</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ITEM034</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Carbonara Oceanica</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5850.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ITEM035</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Quattro Formaggi Quesadilla</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sandwiches, Burgers &amp; Snacks</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3490.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ITEM036</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fisherman's pot</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Soup</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ITEM037</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fresh from the Sea</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>6</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ITEM038</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>San Mig Light</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Beers</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1650.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ITEM039</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Amaretto Sour</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Classic Cocktails</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ITEM040</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Port Barton Sunset</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Signature Cocktails</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>5500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ITEM041</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Blue Ocean Mule</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Signature Cocktails</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3850.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ITEM042</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PATRON REPOSADO 750ML</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>12500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ITEM043</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sizzling Tuna Bites</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sizzlers</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1350.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ITEM044</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ragu Alla Bolognese With Parmesan Espuma</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>4200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ITEM045</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Spiced Cinnamon Apple Spritz</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Signature Cocktails</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1650.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ITEM046</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Salmon Poke</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cold Appetizer</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>5000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ITEM047</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Angus Ribeye</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mains</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>12500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ITEM048</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Crispy Pork Belly</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Mains</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ITEM049</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>San Mig Pale Pilsen</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Beers</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>17</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2550.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ITEM050</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Coke Regular</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sodas &amp; Water</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>240.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ITEM051</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>J. WALKER DOUBLE BLACK Per Shot</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>WHISKY/WHISKEY</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>700.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ITEM052</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Fruity Daiqueri</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Classic Cocktails</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ITEM053</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Fruity Margarita</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Classic Cocktails</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>14</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>4200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ITEM054</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cosmopolitan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Classic Cocktails</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ITEM055</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>fresh Fruit Platter</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ITEM056</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Shakes/Juices</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ITEM057</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>San Mig Pure Malt</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Beers</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>7</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1750.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ITEM058</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Prawn Croquettes</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Crispy Bites</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>800.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ITEM059</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pepperoni</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>6</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>4200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ITEM060</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mango Shake</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ITEM061</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pineapple</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Shakes/Juices</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ITEM062</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Appetizers</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>18</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>414.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ITEM063</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Espresso</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Coffee &amp; Tea</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ITEM064</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cafe Mocha</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Coffee &amp; Tea</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1250.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ITEM065</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Mains</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>180.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ITEM066</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KAYAKING</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ITEM067</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Smoked Buffalo Wings</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Crispy Bites</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>8</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>3200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ITEM068</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tropicale</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1300.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ITEM069</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sunset View - C1 - Main Deck</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ITEM070</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Front Facade - T18 - Main Deck</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ITEM071</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Front Facade - T19 - Main Deck</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ITEM072</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sunset View - C2 - Main Deck</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ITEM073</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sunset View - C3 - Main Deck</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ITEM074</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Caipiranha</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Classic Cocktails</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ITEM075</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ginger-Basil-Cucumber Lemonade</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mocktails</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ITEM076</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Bottled Water</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sodas &amp; Water</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ITEM077</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Coke Zero</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sodas &amp; Water</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>240.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ITEM078</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sprite</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sodas &amp; Water</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1080.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ITEM079</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MAI TAI WD</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Classic Cocktails</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>37</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>11100.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ITEM080</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Mains</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>37</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>55500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ITEM081</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Jacuzzi Couch - C4 - Main Deck</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ITEM082</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Jacuzzi Couch - C7 - Main Deck</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ITEM083</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Front Facade - T1 - Main Deck</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ITEM084</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Daiquiri</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Classic Cocktails</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>600.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ITEM085</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>JOSE CUERVO GOLD 1Lt.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>5500.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Guests</t>
         </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Armie Rose Rey</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cherry Ann Lumactod</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Anna Mae Dela Fuente</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Elaine Dela Cruz</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Dimee Dela Cruz</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Joraly Angeles</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>S007</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Joey Elijan</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Kenneth John Mart Jusos</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>S009</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Rexan Gleem Gaid</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Arjunren Valdez</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_report.xlsx
+++ b/dashboard_report.xlsx
@@ -452,25 +452,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J285"/>
+  <dimension ref="A1:K155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="95" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ALL TRANSACTIONS (FLOATING + MAINLAND)</t>
+          <t>ALL TRANSACTIONS</t>
         </is>
       </c>
     </row>
@@ -518,10 +519,15 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
           <t>Payment</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,12 +566,15 @@
       <c r="H4" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>paypal</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -604,12 +613,15 @@
       <c r="H5" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>paypal</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
@@ -648,12 +660,15 @@
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -692,12 +707,15 @@
       <c r="H7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -736,12 +754,15 @@
       <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -780,12 +801,15 @@
       <c r="H9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -808,7 +832,7 @@
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Anna Mae Dela Fuente, Cashier, Elaine Dela Cruz</t>
+          <t>Elaine Dela Cruz, Anna Mae Dela Fuente, Cashier</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -824,12 +848,15 @@
       <c r="H10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -852,7 +879,7 @@
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Elaine Dela Cruz</t>
+          <t>Elaine Dela Cruz, Cashier</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -868,12 +895,15 @@
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -896,7 +926,7 @@
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Elaine Dela Cruz</t>
+          <t>Elaine Dela Cruz, Cashier</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -912,12 +942,15 @@
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -940,7 +973,7 @@
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Cherry Ann Lumactod, Armie Rose Rey, Dimee Dela Cruz</t>
+          <t>Dimee Dela Cruz, Armie Rose Rey, Cherry Ann Lumactod</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -956,12 +989,15 @@
       <c r="H13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Free of Charge</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -984,7 +1020,7 @@
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Anna Mae Dela Fuente, Cashier, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Anna Mae Dela Fuente, Cashier</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1000,12 +1036,15 @@
       <c r="H14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1044,12 +1083,15 @@
       <c r="H15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1088,12 +1130,15 @@
       <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1116,7 +1161,7 @@
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Cherry Ann Lumactod, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Cherry Ann Lumactod</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1132,12 +1177,15 @@
       <c r="H17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Free of Charge</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1176,12 +1224,15 @@
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1204,7 +1255,7 @@
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Cherry Ann Lumactod, Armie Rose Rey, Cashier</t>
+          <t>Armie Rose Rey, Cherry Ann Lumactod, Cashier</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1220,12 +1271,15 @@
       <c r="H19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1248,7 +1302,7 @@
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Cherry Ann Lumactod, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Cherry Ann Lumactod</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1264,12 +1318,15 @@
       <c r="H20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1308,12 +1365,15 @@
       <c r="H21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1352,12 +1412,15 @@
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1380,7 +1443,7 @@
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Elaine Dela Cruz</t>
+          <t>Elaine Dela Cruz, Cashier</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1396,12 +1459,15 @@
       <c r="H23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1424,7 +1490,7 @@
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Mellan Joy Lapidez, Elaine Dela Cruz</t>
+          <t>Elaine Dela Cruz, Mellan Joy Lapidez</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1440,12 +1506,15 @@
       <c r="H24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1484,12 +1553,15 @@
       <c r="H25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1512,7 +1584,7 @@
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Rexan Gleem Gaid, Cherry Ann Lumactod, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Cherry Ann Lumactod, Rexan Gleem Gaid</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1528,12 +1600,15 @@
       <c r="H26" s="3" t="n">
         <v>3366</v>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>QR PH</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1556,7 +1631,7 @@
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Rexan Gleem Gaid, Cherry Ann Lumactod</t>
+          <t>Cherry Ann Lumactod, Rexan Gleem Gaid</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1572,12 +1647,15 @@
       <c r="H27" s="3" t="n">
         <v>1287</v>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1600,7 +1678,7 @@
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Rexan Gleem Gaid, Anna Mae Dela Fuente, Joey Elijan, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Anna Mae Dela Fuente, Joey Elijan, Rexan Gleem Gaid</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1616,12 +1694,15 @@
       <c r="H28" s="3" t="n">
         <v>8250</v>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1660,12 +1741,15 @@
       <c r="H29" s="3" t="n">
         <v>1980</v>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Free of Charge</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1688,7 +1772,7 @@
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Joey Elijan, Cherry Ann Lumactod, Joraly Angeles, Kenneth John Mart Jusos</t>
+          <t>Joraly Angeles, Kenneth John Mart Jusos, Cherry Ann Lumactod, Joey Elijan</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1704,12 +1788,15 @@
       <c r="H30" s="3" t="n">
         <v>6930.000000000001</v>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>Free of Charge</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1732,7 +1819,7 @@
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Joey Elijan, Kenneth John Mart Jusos, Anna Mae Dela Fuente, Armie Rose Rey, Rexan Gleem Gaid</t>
+          <t>Kenneth John Mart Jusos, Rexan Gleem Gaid, Armie Rose Rey, Anna Mae Dela Fuente, Joey Elijan</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1748,12 +1835,15 @@
       <c r="H31" s="3" t="n">
         <v>80432</v>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Free of Charge</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1792,12 +1882,15 @@
       <c r="H32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1820,7 +1913,7 @@
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Rexan Gleem Gaid, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Rexan Gleem Gaid</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1836,12 +1929,15 @@
       <c r="H33" s="3" t="n">
         <v>3927</v>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>QR PH</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1864,7 +1960,7 @@
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Joey Elijan, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Joey Elijan</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1880,12 +1976,15 @@
       <c r="H34" s="3" t="n">
         <v>3597</v>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>Free of Charge</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1924,12 +2023,15 @@
       <c r="H35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -1964,12 +2066,15 @@
       <c r="H36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2008,12 +2113,15 @@
       <c r="H37" s="3" t="n">
         <v>660</v>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2048,12 +2156,15 @@
       <c r="H38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2088,12 +2199,15 @@
       <c r="H39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2128,12 +2242,15 @@
       <c r="H40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2168,12 +2285,15 @@
       <c r="H41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2208,12 +2328,15 @@
       <c r="H42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2248,12 +2371,15 @@
       <c r="H43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2288,12 +2414,15 @@
       <c r="H44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2332,12 +2461,15 @@
       <c r="H45" s="3" t="n">
         <v>9020</v>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2372,12 +2504,15 @@
       <c r="H46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2412,12 +2547,15 @@
       <c r="H47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2452,12 +2590,15 @@
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2480,7 +2621,7 @@
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Cherry Ann Lumactod, Kenneth John Mart Jusos</t>
+          <t>Kenneth John Mart Jusos, Cherry Ann Lumactod</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2496,12 +2637,15 @@
       <c r="H49" s="3" t="n">
         <v>16324</v>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>Free of Charge</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2540,12 +2684,15 @@
       <c r="H50" s="3" t="n">
         <v>2002</v>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2584,12 +2731,15 @@
       <c r="H51" s="3" t="n">
         <v>1320</v>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2612,7 +2762,7 @@
       <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Krisia Favila, Anna Mae Dela Fuente</t>
+          <t>Anna Mae Dela Fuente, Krisia Favila</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2628,12 +2778,15 @@
       <c r="H52" s="3" t="n">
         <v>3432</v>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2672,12 +2825,15 @@
       <c r="H53" s="3" t="n">
         <v>2497</v>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>QR PH</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2716,12 +2872,15 @@
       <c r="H54" s="3" t="n">
         <v>4290</v>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2744,7 +2903,7 @@
       <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Anna Mae Dela Fuente, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Anna Mae Dela Fuente</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2760,12 +2919,15 @@
       <c r="H55" s="3" t="n">
         <v>2970</v>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2804,12 +2966,15 @@
       <c r="H56" s="3" t="n">
         <v>1320</v>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2848,12 +3013,15 @@
       <c r="H57" s="3" t="n">
         <v>3179</v>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2892,12 +3060,15 @@
       <c r="H58" s="3" t="n">
         <v>1100</v>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>Free of Charge</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="K58" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2936,12 +3107,15 @@
       <c r="H59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -2980,12 +3154,15 @@
       <c r="H60" s="3" t="n">
         <v>1980</v>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3008,7 +3185,7 @@
       <c r="D61" s="3" t="n"/>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Krisia Favila, Joraly Angeles</t>
+          <t>Joraly Angeles, Krisia Favila</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3024,12 +3201,15 @@
       <c r="H61" s="3" t="n">
         <v>990.0000000000001</v>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="K61" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3068,12 +3248,15 @@
       <c r="H62" s="3" t="n">
         <v>1320</v>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="K62" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3112,12 +3295,15 @@
       <c r="H63" s="3" t="n">
         <v>3597</v>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3140,7 +3326,7 @@
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Krisia Favila, Anna Mae Dela Fuente, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Anna Mae Dela Fuente, Krisia Favila</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3156,12 +3342,15 @@
       <c r="H64" s="3" t="n">
         <v>2145</v>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3196,12 +3385,15 @@
       <c r="H65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I65" s="3" t="inlineStr">
+      <c r="I65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J65" s="3" t="inlineStr">
+      <c r="K65" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3236,12 +3428,15 @@
       <c r="H66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="I66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -3276,12 +3471,15 @@
       <c r="H67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr">
+      <c r="K67" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -3316,12 +3514,15 @@
       <c r="H68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="K68" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -3356,12 +3557,15 @@
       <c r="H69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="K69" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -3396,12 +3600,15 @@
       <c r="H70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="I70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J70" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -3440,12 +3647,15 @@
       <c r="H71" s="3" t="n">
         <v>12914</v>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr">
+      <c r="K71" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3484,12 +3694,15 @@
       <c r="H72" s="3" t="n">
         <v>4345</v>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="I72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="K72" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3528,12 +3741,15 @@
       <c r="H73" s="3" t="n">
         <v>660</v>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="K73" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3572,12 +3788,15 @@
       <c r="H74" s="3" t="n">
         <v>4576</v>
       </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="I74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>Free of Charge</t>
         </is>
       </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="K74" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3612,12 +3831,15 @@
       <c r="H75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="I75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="K75" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -3652,12 +3874,15 @@
       <c r="H76" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="K76" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -3696,12 +3921,15 @@
       <c r="H77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J77" s="3" t="inlineStr">
+      <c r="K77" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3736,12 +3964,15 @@
       <c r="H78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
@@ -3776,12 +4007,15 @@
       <c r="H79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="K79" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -3804,7 +4038,7 @@
       <c r="D80" s="3" t="n"/>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Krisia Favila, Kenneth John Mart Jusos</t>
+          <t>Kenneth John Mart Jusos, Krisia Favila</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3820,12 +4054,15 @@
       <c r="H80" s="3" t="n">
         <v>1947</v>
       </c>
-      <c r="I80" s="3" t="inlineStr">
+      <c r="I80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
         <is>
           <t>QR PH</t>
         </is>
       </c>
-      <c r="J80" s="3" t="inlineStr">
+      <c r="K80" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3864,12 +4101,15 @@
       <c r="H81" s="3" t="n">
         <v>2420</v>
       </c>
-      <c r="I81" s="3" t="inlineStr">
+      <c r="I81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J81" s="3" t="inlineStr">
+      <c r="K81" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3908,12 +4148,15 @@
       <c r="H82" s="3" t="n">
         <v>440.0000000000001</v>
       </c>
-      <c r="I82" s="3" t="inlineStr">
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J82" s="3" t="inlineStr">
+      <c r="K82" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3952,12 +4195,15 @@
       <c r="H83" s="3" t="n">
         <v>660</v>
       </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="I83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="K83" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -3996,12 +4242,15 @@
       <c r="H84" s="3" t="n">
         <v>605</v>
       </c>
-      <c r="I84" s="3" t="inlineStr">
+      <c r="I84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J84" s="3" t="inlineStr">
+      <c r="K84" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4040,12 +4289,15 @@
       <c r="H85" s="3" t="n">
         <v>605</v>
       </c>
-      <c r="I85" s="3" t="inlineStr">
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr">
+      <c r="K85" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4080,12 +4332,15 @@
       <c r="H86" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="3" t="inlineStr">
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J86" s="3" t="inlineStr">
+      <c r="K86" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4120,12 +4375,15 @@
       <c r="H87" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="3" t="inlineStr">
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J87" s="3" t="inlineStr">
+      <c r="K87" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4160,12 +4418,15 @@
       <c r="H88" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J88" s="3" t="inlineStr">
+      <c r="K88" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4200,12 +4461,15 @@
       <c r="H89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I89" s="3" t="inlineStr">
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J89" s="3" t="inlineStr">
+      <c r="K89" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4244,12 +4508,15 @@
       <c r="H90" s="3" t="n">
         <v>1386</v>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="I90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="K90" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4288,12 +4555,15 @@
       <c r="H91" s="3" t="n">
         <v>1034</v>
       </c>
-      <c r="I91" s="3" t="inlineStr">
+      <c r="I91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>QR PH</t>
         </is>
       </c>
-      <c r="J91" s="3" t="inlineStr">
+      <c r="K91" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4332,12 +4602,15 @@
       <c r="H92" s="3" t="n">
         <v>1595</v>
       </c>
-      <c r="I92" s="3" t="inlineStr">
+      <c r="I92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J92" s="3" t="inlineStr">
+      <c r="K92" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4372,12 +4645,15 @@
       <c r="H93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I93" s="3" t="inlineStr">
+      <c r="I93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J93" s="3" t="inlineStr">
+      <c r="K93" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4416,12 +4692,15 @@
       <c r="H94" s="3" t="n">
         <v>3630</v>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J94" s="3" t="inlineStr">
+      <c r="K94" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4460,12 +4739,15 @@
       <c r="H95" s="3" t="n">
         <v>2750</v>
       </c>
-      <c r="I95" s="3" t="inlineStr">
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="J95" s="3" t="inlineStr">
+      <c r="K95" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4500,12 +4782,15 @@
       <c r="H96" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I96" s="3" t="inlineStr">
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J96" s="3" t="inlineStr">
+      <c r="K96" s="3" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -4540,12 +4825,15 @@
       <c r="H97" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I97" s="3" t="inlineStr">
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J97" s="3" t="inlineStr">
+      <c r="K97" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4580,12 +4868,15 @@
       <c r="H98" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="I98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J98" s="3" t="inlineStr">
+      <c r="K98" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4620,12 +4911,15 @@
       <c r="H99" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I99" s="3" t="inlineStr">
+      <c r="I99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J99" s="3" t="inlineStr">
+      <c r="K99" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4660,12 +4954,15 @@
       <c r="H100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="3" t="inlineStr">
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J100" s="3" t="inlineStr">
+      <c r="K100" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4700,12 +4997,15 @@
       <c r="H101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="inlineStr">
+      <c r="I101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J101" s="3" t="inlineStr">
+      <c r="K101" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4740,12 +5040,15 @@
       <c r="H102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J102" s="3" t="inlineStr">
+      <c r="K102" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4780,12 +5083,15 @@
       <c r="H103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="3" t="inlineStr">
+      <c r="I103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="J103" s="3" t="inlineStr">
+      <c r="K103" s="3" t="inlineStr">
         <is>
           <t>billout</t>
         </is>
@@ -4806,7 +5112,11 @@
           <t>Floating Net Sales</t>
         </is>
       </c>
-      <c r="B107" s="2" t="n"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Total Discount</t>
+        </is>
+      </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n"/>
       <c r="E107" s="2" t="n"/>
@@ -4815,12 +5125,15 @@
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="n"/>
       <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B108" s="3" t="n"/>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C108" s="3" t="n"/>
       <c r="D108" s="3" t="n"/>
       <c r="E108" s="3" t="n"/>
@@ -4829,6 +5142,7 @@
       <c r="H108" s="3" t="n"/>
       <c r="I108" s="3" t="n"/>
       <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="n"/>
     </row>
     <row r="109"/>
     <row r="110">
@@ -4858,112 +5172,147 @@
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="n"/>
       <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="n"/>
     </row>
     <row r="111"/>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="n"/>
-      <c r="F112" s="2" t="n"/>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="n"/>
-      <c r="J112" s="2" t="n"/>
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>YESTERDAY</t>
+        </is>
+      </c>
     </row>
     <row r="113"/>
     <row r="114">
-      <c r="A114" s="1" t="inlineStr">
-        <is>
-          <t>YESTERDAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="115"/>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Floating Net Sales</t>
         </is>
       </c>
-      <c r="B116" s="2" t="n"/>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="n"/>
-      <c r="G116" s="2" t="n"/>
-      <c r="H116" s="2" t="n"/>
-      <c r="I116" s="2" t="n"/>
-      <c r="J116" s="2" t="n"/>
-    </row>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Total Discount</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2" t="n"/>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>15125</v>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n"/>
+      <c r="D115" s="3" t="n"/>
+      <c r="E115" s="3" t="n"/>
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="3" t="n"/>
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="n"/>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="n"/>
+    </row>
+    <row r="116"/>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="2" t="n"/>
+      <c r="H117" s="2" t="n"/>
+      <c r="I117" s="2" t="n"/>
+      <c r="J117" s="2" t="n"/>
+      <c r="K117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n"/>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>cashier</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
         <v>15125</v>
       </c>
-      <c r="B117" s="3" t="n"/>
-      <c r="C117" s="3" t="n"/>
-      <c r="D117" s="3" t="n"/>
-      <c r="E117" s="3" t="n"/>
-      <c r="F117" s="3" t="n"/>
-      <c r="G117" s="3" t="n"/>
-      <c r="H117" s="3" t="n"/>
-      <c r="I117" s="3" t="n"/>
-      <c r="J117" s="3" t="n"/>
-    </row>
-    <row r="118"/>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n"/>
+      <c r="F118" s="3" t="n"/>
+      <c r="G118" s="3" t="n"/>
+      <c r="H118" s="3" t="n"/>
+      <c r="I118" s="3" t="n"/>
+      <c r="J118" s="3" t="n"/>
+      <c r="K118" s="3" t="n"/>
+    </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Items</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="n"/>
-      <c r="F119" s="2" t="n"/>
-      <c r="G119" s="2" t="n"/>
-      <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="n"/>
-      <c r="J119" s="2" t="n"/>
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Anna Mae Dela Fuente</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>3150</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E119" s="3" t="n"/>
+      <c r="F119" s="3" t="n"/>
+      <c r="G119" s="3" t="n"/>
+      <c r="H119" s="3" t="n"/>
+      <c r="I119" s="3" t="n"/>
+      <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n"/>
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Joey Elijan</t>
+        </is>
+      </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>cashier</t>
+          <t>waiter</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>15125</v>
+        <v>1540</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E120" s="3" t="n"/>
       <c r="F120" s="3" t="n"/>
@@ -4971,11 +5320,12 @@
       <c r="H120" s="3" t="n"/>
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Anna Mae Dela Fuente</t>
+          <t>Armie Rose Rey</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4984,10 +5334,10 @@
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>3150</v>
+        <v>3050</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n"/>
@@ -4995,11 +5345,12 @@
       <c r="H121" s="3" t="n"/>
       <c r="I121" s="3" t="n"/>
       <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Joey Elijan</t>
+          <t>Daizer Raye Paglicawan</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5008,7 +5359,7 @@
         </is>
       </c>
       <c r="C122" s="3" t="n">
-        <v>1540</v>
+        <v>1020</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>4</v>
@@ -5019,11 +5370,12 @@
       <c r="H122" s="3" t="n"/>
       <c r="I122" s="3" t="n"/>
       <c r="J122" s="3" t="n"/>
+      <c r="K122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey</t>
+          <t>Joraly Angeles</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -5032,10 +5384,10 @@
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>3050</v>
+        <v>4750</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E123" s="3" t="n"/>
       <c r="F123" s="3" t="n"/>
@@ -5043,72 +5395,29 @@
       <c r="H123" s="3" t="n"/>
       <c r="I123" s="3" t="n"/>
       <c r="J123" s="3" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>Daizer Raye Paglicawan</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>1020</v>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E124" s="3" t="n"/>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="3" t="n"/>
-      <c r="H124" s="3" t="n"/>
-      <c r="I124" s="3" t="n"/>
-      <c r="J124" s="3" t="n"/>
-    </row>
+      <c r="K123" s="3" t="n"/>
+    </row>
+    <row r="124"/>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>Joraly Angeles</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>4750</v>
-      </c>
-      <c r="D125" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E125" s="3" t="n"/>
-      <c r="F125" s="3" t="n"/>
-      <c r="G125" s="3" t="n"/>
-      <c r="H125" s="3" t="n"/>
-      <c r="I125" s="3" t="n"/>
-      <c r="J125" s="3" t="n"/>
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>THIS WEEK</t>
+        </is>
+      </c>
     </row>
     <row r="126"/>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Floating Net Sales</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+          <t>Total Discount</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n"/>
       <c r="E127" s="2" t="n"/>
       <c r="F127" s="2" t="n"/>
@@ -5116,19 +5425,16 @@
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="n"/>
       <c r="J127" s="2" t="n"/>
+      <c r="K127" s="2" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>Tuna Crudo</t>
-        </is>
+      <c r="A128" s="3" t="n">
+        <v>17072</v>
       </c>
       <c r="B128" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C128" s="3" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n"/>
       <c r="D128" s="3" t="n"/>
       <c r="E128" s="3" t="n"/>
       <c r="F128" s="3" t="n"/>
@@ -5136,299 +5442,272 @@
       <c r="H128" s="3" t="n"/>
       <c r="I128" s="3" t="n"/>
       <c r="J128" s="3" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>Prawn Croquettes</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="D129" s="3" t="n"/>
-      <c r="E129" s="3" t="n"/>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="3" t="n"/>
-      <c r="H129" s="3" t="n"/>
-      <c r="I129" s="3" t="n"/>
-      <c r="J129" s="3" t="n"/>
-    </row>
+      <c r="K128" s="3" t="n"/>
+    </row>
+    <row r="129"/>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>Ginger-Basil-Cucumber Lemonade</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C130" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D130" s="3" t="n"/>
-      <c r="E130" s="3" t="n"/>
-      <c r="F130" s="3" t="n"/>
-      <c r="G130" s="3" t="n"/>
-      <c r="H130" s="3" t="n"/>
-      <c r="I130" s="3" t="n"/>
-      <c r="J130" s="3" t="n"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+      <c r="J130" s="2" t="n"/>
+      <c r="K130" s="2" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>BOTTLED WATER 500 ML</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="n">
-        <v>1</v>
+      <c r="A131" s="3" t="n"/>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>cashier</t>
+        </is>
       </c>
       <c r="C131" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D131" s="3" t="n"/>
+        <v>17072</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E131" s="3" t="n"/>
       <c r="F131" s="3" t="n"/>
       <c r="G131" s="3" t="n"/>
       <c r="H131" s="3" t="n"/>
       <c r="I131" s="3" t="n"/>
       <c r="J131" s="3" t="n"/>
+      <c r="K131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>Tropicale</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="n">
+          <t>Krisia Favila</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C132" s="3" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D132" s="3" t="n"/>
       <c r="E132" s="3" t="n"/>
       <c r="F132" s="3" t="n"/>
       <c r="G132" s="3" t="n"/>
       <c r="H132" s="3" t="n"/>
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="n"/>
+      <c r="K132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Pineapple</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="n">
-        <v>1</v>
+          <t>Kenneth John Mart Jusos</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="D133" s="3" t="n"/>
+        <v>1770</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="E133" s="3" t="n"/>
       <c r="F133" s="3" t="n"/>
       <c r="G133" s="3" t="n"/>
       <c r="H133" s="3" t="n"/>
       <c r="I133" s="3" t="n"/>
       <c r="J133" s="3" t="n"/>
+      <c r="K133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>Cafe Latte</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="n">
-        <v>2</v>
+          <t>Anna Mae Dela Fuente</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="D134" s="3" t="n"/>
+        <v>3150</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="E134" s="3" t="n"/>
       <c r="F134" s="3" t="n"/>
       <c r="G134" s="3" t="n"/>
       <c r="H134" s="3" t="n"/>
       <c r="I134" s="3" t="n"/>
       <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>San Mig Pale Pilsen</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="n">
-        <v>1</v>
+          <t>Joey Elijan</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="D135" s="3" t="n"/>
+        <v>1540</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="E135" s="3" t="n"/>
       <c r="F135" s="3" t="n"/>
       <c r="G135" s="3" t="n"/>
       <c r="H135" s="3" t="n"/>
       <c r="I135" s="3" t="n"/>
       <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>Margherita</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="n">
-        <v>1</v>
+          <t>Armie Rose Rey</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C136" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D136" s="3" t="n"/>
+        <v>3050</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="E136" s="3" t="n"/>
       <c r="F136" s="3" t="n"/>
       <c r="G136" s="3" t="n"/>
       <c r="H136" s="3" t="n"/>
       <c r="I136" s="3" t="n"/>
       <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Blue Ocean Mule</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="n">
-        <v>5</v>
+          <t>Daizer Raye Paglicawan</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C137" s="3" t="n">
-        <v>2750</v>
-      </c>
-      <c r="D137" s="3" t="n"/>
+        <v>1020</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="E137" s="3" t="n"/>
       <c r="F137" s="3" t="n"/>
       <c r="G137" s="3" t="n"/>
       <c r="H137" s="3" t="n"/>
       <c r="I137" s="3" t="n"/>
       <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>TANDUAY RUM</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="n">
-        <v>1</v>
+          <t>Joraly Angeles</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C138" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="D138" s="3" t="n"/>
+        <v>4750</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="E138" s="3" t="n"/>
       <c r="F138" s="3" t="n"/>
       <c r="G138" s="3" t="n"/>
       <c r="H138" s="3" t="n"/>
       <c r="I138" s="3" t="n"/>
       <c r="J138" s="3" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>COKE REGULAR</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C139" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="D139" s="3" t="n"/>
-      <c r="E139" s="3" t="n"/>
-      <c r="F139" s="3" t="n"/>
-      <c r="G139" s="3" t="n"/>
-      <c r="H139" s="3" t="n"/>
-      <c r="I139" s="3" t="n"/>
-      <c r="J139" s="3" t="n"/>
-    </row>
+      <c r="K138" s="3" t="n"/>
+    </row>
+    <row r="139"/>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>Surf &amp; Turf Burger</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="3" t="n">
-        <v>670</v>
-      </c>
-      <c r="D140" s="3" t="n"/>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n"/>
-      <c r="G140" s="3" t="n"/>
-      <c r="H140" s="3" t="n"/>
-      <c r="I140" s="3" t="n"/>
-      <c r="J140" s="3" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Coke Zero</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="D141" s="3" t="n"/>
-      <c r="E141" s="3" t="n"/>
-      <c r="F141" s="3" t="n"/>
-      <c r="G141" s="3" t="n"/>
-      <c r="H141" s="3" t="n"/>
-      <c r="I141" s="3" t="n"/>
-      <c r="J141" s="3" t="n"/>
-    </row>
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>THIS MONTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="141"/>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>San Mig Apple</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="D142" s="3" t="n"/>
-      <c r="E142" s="3" t="n"/>
-      <c r="F142" s="3" t="n"/>
-      <c r="G142" s="3" t="n"/>
-      <c r="H142" s="3" t="n"/>
-      <c r="I142" s="3" t="n"/>
-      <c r="J142" s="3" t="n"/>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Floating Net Sales</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Total Discount</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="n"/>
+      <c r="H142" s="2" t="n"/>
+      <c r="I142" s="2" t="n"/>
+      <c r="J142" s="2" t="n"/>
+      <c r="K142" s="2" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Smoked Buffalo Wings</t>
-        </is>
+      <c r="A143" s="3" t="n">
+        <v>207482</v>
       </c>
       <c r="B143" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="3" t="n">
-        <v>400</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C143" s="3" t="n"/>
       <c r="D143" s="3" t="n"/>
       <c r="E143" s="3" t="n"/>
       <c r="F143" s="3" t="n"/>
@@ -5436,2744 +5715,291 @@
       <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="n"/>
       <c r="J143" s="3" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>Pepperoni</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C144" s="3" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D144" s="3" t="n"/>
-      <c r="E144" s="3" t="n"/>
-      <c r="F144" s="3" t="n"/>
-      <c r="G144" s="3" t="n"/>
-      <c r="H144" s="3" t="n"/>
-      <c r="I144" s="3" t="n"/>
-      <c r="J144" s="3" t="n"/>
-    </row>
+      <c r="K143" s="3" t="n"/>
+    </row>
+    <row r="144"/>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>TANQUERAY Per Shot</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="D145" s="3" t="n"/>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n"/>
-      <c r="G145" s="3" t="n"/>
-      <c r="H145" s="3" t="n"/>
-      <c r="I145" s="3" t="n"/>
-      <c r="J145" s="3" t="n"/>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="2" t="n"/>
+      <c r="H145" s="2" t="n"/>
+      <c r="I145" s="2" t="n"/>
+      <c r="J145" s="2" t="n"/>
+      <c r="K145" s="2" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>Spiced Cinnamon Apple Spritz</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="n">
-        <v>1</v>
+      <c r="A146" s="3" t="n"/>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>cashier</t>
+        </is>
       </c>
       <c r="C146" s="3" t="n">
-        <v>550</v>
-      </c>
-      <c r="D146" s="3" t="n"/>
+        <v>207482</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E146" s="3" t="n"/>
       <c r="F146" s="3" t="n"/>
       <c r="G146" s="3" t="n"/>
       <c r="H146" s="3" t="n"/>
       <c r="I146" s="3" t="n"/>
       <c r="J146" s="3" t="n"/>
+      <c r="K146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>Amaretto Sour</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="n">
-        <v>1</v>
+          <t>Armie Rose Rey</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C147" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D147" s="3" t="n"/>
+        <v>26540</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>151</v>
+      </c>
       <c r="E147" s="3" t="n"/>
       <c r="F147" s="3" t="n"/>
       <c r="G147" s="3" t="n"/>
       <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="n"/>
       <c r="J147" s="3" t="n"/>
+      <c r="K147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>Port Barton Sunset</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="n">
-        <v>2</v>
+          <t>Rexan Gleem Gaid</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C148" s="3" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D148" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="E148" s="3" t="n"/>
       <c r="F148" s="3" t="n"/>
       <c r="G148" s="3" t="n"/>
       <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="n"/>
       <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>Pinacolada</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="n">
-        <v>1</v>
+          <t>Cherry Ann Lumactod</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C149" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D149" s="3" t="n"/>
+        <v>7700</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>33</v>
+      </c>
       <c r="E149" s="3" t="n"/>
       <c r="F149" s="3" t="n"/>
       <c r="G149" s="3" t="n"/>
       <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="n"/>
       <c r="J149" s="3" t="n"/>
+      <c r="K149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>Sex On The Beach</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="n">
-        <v>1</v>
+          <t>Anna Mae Dela Fuente</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
       </c>
       <c r="C150" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D150" s="3" t="n"/>
+        <v>20390</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>84</v>
+      </c>
       <c r="E150" s="3" t="n"/>
       <c r="F150" s="3" t="n"/>
       <c r="G150" s="3" t="n"/>
       <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="n"/>
       <c r="J150" s="3" t="n"/>
-    </row>
-    <row r="151"/>
+      <c r="K150" s="3" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Joey Elijan</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>13890</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="E151" s="3" t="n"/>
+      <c r="F151" s="3" t="n"/>
+      <c r="G151" s="3" t="n"/>
+      <c r="H151" s="3" t="n"/>
+      <c r="I151" s="3" t="n"/>
+      <c r="J151" s="3" t="n"/>
+      <c r="K151" s="3" t="n"/>
+    </row>
     <row r="152">
-      <c r="A152" s="1" t="inlineStr">
-        <is>
-          <t>THIS WEEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="153"/>
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Joraly Angeles</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>6500</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="3" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="3" t="n"/>
+      <c r="I152" s="3" t="n"/>
+      <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Kenneth John Mart Jusos</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>22310</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="E153" s="3" t="n"/>
+      <c r="F153" s="3" t="n"/>
+      <c r="G153" s="3" t="n"/>
+      <c r="H153" s="3" t="n"/>
+      <c r="I153" s="3" t="n"/>
+      <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="n"/>
+    </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Floating Net Sales</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="n"/>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" s="2" t="n"/>
-      <c r="F154" s="2" t="n"/>
-      <c r="G154" s="2" t="n"/>
-      <c r="H154" s="2" t="n"/>
-      <c r="I154" s="2" t="n"/>
-      <c r="J154" s="2" t="n"/>
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Krisia Favila</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
+      <c r="I154" s="3" t="n"/>
+      <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="n">
-        <v>17072</v>
-      </c>
-      <c r="B155" s="3" t="n"/>
-      <c r="C155" s="3" t="n"/>
-      <c r="D155" s="3" t="n"/>
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Daizer Raye Paglicawan</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="E155" s="3" t="n"/>
       <c r="F155" s="3" t="n"/>
       <c r="G155" s="3" t="n"/>
       <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="n"/>
       <c r="J155" s="3" t="n"/>
-    </row>
-    <row r="156"/>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>Items</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="n"/>
-      <c r="F157" s="2" t="n"/>
-      <c r="G157" s="2" t="n"/>
-      <c r="H157" s="2" t="n"/>
-      <c r="I157" s="2" t="n"/>
-      <c r="J157" s="2" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="n"/>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>cashier</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="n">
-        <v>17072</v>
-      </c>
-      <c r="D158" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" s="3" t="n"/>
-      <c r="F158" s="3" t="n"/>
-      <c r="G158" s="3" t="n"/>
-      <c r="H158" s="3" t="n"/>
-      <c r="I158" s="3" t="n"/>
-      <c r="J158" s="3" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>Krisia Favila</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E159" s="3" t="n"/>
-      <c r="F159" s="3" t="n"/>
-      <c r="G159" s="3" t="n"/>
-      <c r="H159" s="3" t="n"/>
-      <c r="I159" s="3" t="n"/>
-      <c r="J159" s="3" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>Kenneth John Mart Jusos</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="n">
-        <v>1770</v>
-      </c>
-      <c r="D160" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E160" s="3" t="n"/>
-      <c r="F160" s="3" t="n"/>
-      <c r="G160" s="3" t="n"/>
-      <c r="H160" s="3" t="n"/>
-      <c r="I160" s="3" t="n"/>
-      <c r="J160" s="3" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>Anna Mae Dela Fuente</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="n">
-        <v>3150</v>
-      </c>
-      <c r="D161" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E161" s="3" t="n"/>
-      <c r="F161" s="3" t="n"/>
-      <c r="G161" s="3" t="n"/>
-      <c r="H161" s="3" t="n"/>
-      <c r="I161" s="3" t="n"/>
-      <c r="J161" s="3" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>Joey Elijan</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v>1540</v>
-      </c>
-      <c r="D162" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E162" s="3" t="n"/>
-      <c r="F162" s="3" t="n"/>
-      <c r="G162" s="3" t="n"/>
-      <c r="H162" s="3" t="n"/>
-      <c r="I162" s="3" t="n"/>
-      <c r="J162" s="3" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>Armie Rose Rey</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="n">
-        <v>3050</v>
-      </c>
-      <c r="D163" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E163" s="3" t="n"/>
-      <c r="F163" s="3" t="n"/>
-      <c r="G163" s="3" t="n"/>
-      <c r="H163" s="3" t="n"/>
-      <c r="I163" s="3" t="n"/>
-      <c r="J163" s="3" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>Daizer Raye Paglicawan</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="n">
-        <v>1020</v>
-      </c>
-      <c r="D164" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E164" s="3" t="n"/>
-      <c r="F164" s="3" t="n"/>
-      <c r="G164" s="3" t="n"/>
-      <c r="H164" s="3" t="n"/>
-      <c r="I164" s="3" t="n"/>
-      <c r="J164" s="3" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>Joraly Angeles</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="n">
-        <v>4750</v>
-      </c>
-      <c r="D165" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E165" s="3" t="n"/>
-      <c r="F165" s="3" t="n"/>
-      <c r="G165" s="3" t="n"/>
-      <c r="H165" s="3" t="n"/>
-      <c r="I165" s="3" t="n"/>
-      <c r="J165" s="3" t="n"/>
-    </row>
-    <row r="166"/>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" s="2" t="n"/>
-      <c r="F167" s="2" t="n"/>
-      <c r="G167" s="2" t="n"/>
-      <c r="H167" s="2" t="n"/>
-      <c r="I167" s="2" t="n"/>
-      <c r="J167" s="2" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>Sunset View - C1 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C168" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" s="3" t="n"/>
-      <c r="E168" s="3" t="n"/>
-      <c r="F168" s="3" t="n"/>
-      <c r="G168" s="3" t="n"/>
-      <c r="H168" s="3" t="n"/>
-      <c r="I168" s="3" t="n"/>
-      <c r="J168" s="3" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>Fruity Margarita</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C169" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D169" s="3" t="n"/>
-      <c r="E169" s="3" t="n"/>
-      <c r="F169" s="3" t="n"/>
-      <c r="G169" s="3" t="n"/>
-      <c r="H169" s="3" t="n"/>
-      <c r="I169" s="3" t="n"/>
-      <c r="J169" s="3" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>Port Barton Sunset</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C170" s="3" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D170" s="3" t="n"/>
-      <c r="E170" s="3" t="n"/>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="3" t="n"/>
-      <c r="H170" s="3" t="n"/>
-      <c r="I170" s="3" t="n"/>
-      <c r="J170" s="3" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>Front Facade - T4 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C171" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" s="3" t="n"/>
-      <c r="E171" s="3" t="n"/>
-      <c r="F171" s="3" t="n"/>
-      <c r="G171" s="3" t="n"/>
-      <c r="H171" s="3" t="n"/>
-      <c r="I171" s="3" t="n"/>
-      <c r="J171" s="3" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>Bottled Water</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C172" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D172" s="3" t="n"/>
-      <c r="E172" s="3" t="n"/>
-      <c r="F172" s="3" t="n"/>
-      <c r="G172" s="3" t="n"/>
-      <c r="H172" s="3" t="n"/>
-      <c r="I172" s="3" t="n"/>
-      <c r="J172" s="3" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>Surf &amp; Turf Burger</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C173" s="3" t="n">
-        <v>1340</v>
-      </c>
-      <c r="D173" s="3" t="n"/>
-      <c r="E173" s="3" t="n"/>
-      <c r="F173" s="3" t="n"/>
-      <c r="G173" s="3" t="n"/>
-      <c r="H173" s="3" t="n"/>
-      <c r="I173" s="3" t="n"/>
-      <c r="J173" s="3" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>San Mig Light</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C174" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="D174" s="3" t="n"/>
-      <c r="E174" s="3" t="n"/>
-      <c r="F174" s="3" t="n"/>
-      <c r="G174" s="3" t="n"/>
-      <c r="H174" s="3" t="n"/>
-      <c r="I174" s="3" t="n"/>
-      <c r="J174" s="3" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>Tuna Crudo</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C175" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="D175" s="3" t="n"/>
-      <c r="E175" s="3" t="n"/>
-      <c r="F175" s="3" t="n"/>
-      <c r="G175" s="3" t="n"/>
-      <c r="H175" s="3" t="n"/>
-      <c r="I175" s="3" t="n"/>
-      <c r="J175" s="3" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>Prawn Croquettes</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C176" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="D176" s="3" t="n"/>
-      <c r="E176" s="3" t="n"/>
-      <c r="F176" s="3" t="n"/>
-      <c r="G176" s="3" t="n"/>
-      <c r="H176" s="3" t="n"/>
-      <c r="I176" s="3" t="n"/>
-      <c r="J176" s="3" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>Ginger-Basil-Cucumber Lemonade</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C177" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D177" s="3" t="n"/>
-      <c r="E177" s="3" t="n"/>
-      <c r="F177" s="3" t="n"/>
-      <c r="G177" s="3" t="n"/>
-      <c r="H177" s="3" t="n"/>
-      <c r="I177" s="3" t="n"/>
-      <c r="J177" s="3" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>BOTTLED WATER 500 ML</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C178" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D178" s="3" t="n"/>
-      <c r="E178" s="3" t="n"/>
-      <c r="F178" s="3" t="n"/>
-      <c r="G178" s="3" t="n"/>
-      <c r="H178" s="3" t="n"/>
-      <c r="I178" s="3" t="n"/>
-      <c r="J178" s="3" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>Tropicale</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C179" s="3" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D179" s="3" t="n"/>
-      <c r="E179" s="3" t="n"/>
-      <c r="F179" s="3" t="n"/>
-      <c r="G179" s="3" t="n"/>
-      <c r="H179" s="3" t="n"/>
-      <c r="I179" s="3" t="n"/>
-      <c r="J179" s="3" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>Pineapple</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C180" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="D180" s="3" t="n"/>
-      <c r="E180" s="3" t="n"/>
-      <c r="F180" s="3" t="n"/>
-      <c r="G180" s="3" t="n"/>
-      <c r="H180" s="3" t="n"/>
-      <c r="I180" s="3" t="n"/>
-      <c r="J180" s="3" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>Cafe Latte</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C181" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="D181" s="3" t="n"/>
-      <c r="E181" s="3" t="n"/>
-      <c r="F181" s="3" t="n"/>
-      <c r="G181" s="3" t="n"/>
-      <c r="H181" s="3" t="n"/>
-      <c r="I181" s="3" t="n"/>
-      <c r="J181" s="3" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>San Mig Pale Pilsen</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C182" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="D182" s="3" t="n"/>
-      <c r="E182" s="3" t="n"/>
-      <c r="F182" s="3" t="n"/>
-      <c r="G182" s="3" t="n"/>
-      <c r="H182" s="3" t="n"/>
-      <c r="I182" s="3" t="n"/>
-      <c r="J182" s="3" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>Margherita</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C183" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D183" s="3" t="n"/>
-      <c r="E183" s="3" t="n"/>
-      <c r="F183" s="3" t="n"/>
-      <c r="G183" s="3" t="n"/>
-      <c r="H183" s="3" t="n"/>
-      <c r="I183" s="3" t="n"/>
-      <c r="J183" s="3" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="inlineStr">
-        <is>
-          <t>Blue Ocean Mule</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C184" s="3" t="n">
-        <v>2750</v>
-      </c>
-      <c r="D184" s="3" t="n"/>
-      <c r="E184" s="3" t="n"/>
-      <c r="F184" s="3" t="n"/>
-      <c r="G184" s="3" t="n"/>
-      <c r="H184" s="3" t="n"/>
-      <c r="I184" s="3" t="n"/>
-      <c r="J184" s="3" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>TANDUAY RUM</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C185" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="D185" s="3" t="n"/>
-      <c r="E185" s="3" t="n"/>
-      <c r="F185" s="3" t="n"/>
-      <c r="G185" s="3" t="n"/>
-      <c r="H185" s="3" t="n"/>
-      <c r="I185" s="3" t="n"/>
-      <c r="J185" s="3" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>COKE REGULAR</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C186" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="D186" s="3" t="n"/>
-      <c r="E186" s="3" t="n"/>
-      <c r="F186" s="3" t="n"/>
-      <c r="G186" s="3" t="n"/>
-      <c r="H186" s="3" t="n"/>
-      <c r="I186" s="3" t="n"/>
-      <c r="J186" s="3" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>Coke Zero</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C187" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="D187" s="3" t="n"/>
-      <c r="E187" s="3" t="n"/>
-      <c r="F187" s="3" t="n"/>
-      <c r="G187" s="3" t="n"/>
-      <c r="H187" s="3" t="n"/>
-      <c r="I187" s="3" t="n"/>
-      <c r="J187" s="3" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>San Mig Apple</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C188" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="D188" s="3" t="n"/>
-      <c r="E188" s="3" t="n"/>
-      <c r="F188" s="3" t="n"/>
-      <c r="G188" s="3" t="n"/>
-      <c r="H188" s="3" t="n"/>
-      <c r="I188" s="3" t="n"/>
-      <c r="J188" s="3" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>Smoked Buffalo Wings</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C189" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="D189" s="3" t="n"/>
-      <c r="E189" s="3" t="n"/>
-      <c r="F189" s="3" t="n"/>
-      <c r="G189" s="3" t="n"/>
-      <c r="H189" s="3" t="n"/>
-      <c r="I189" s="3" t="n"/>
-      <c r="J189" s="3" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>Pepperoni</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C190" s="3" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D190" s="3" t="n"/>
-      <c r="E190" s="3" t="n"/>
-      <c r="F190" s="3" t="n"/>
-      <c r="G190" s="3" t="n"/>
-      <c r="H190" s="3" t="n"/>
-      <c r="I190" s="3" t="n"/>
-      <c r="J190" s="3" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="inlineStr">
-        <is>
-          <t>TANQUERAY Per Shot</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C191" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="D191" s="3" t="n"/>
-      <c r="E191" s="3" t="n"/>
-      <c r="F191" s="3" t="n"/>
-      <c r="G191" s="3" t="n"/>
-      <c r="H191" s="3" t="n"/>
-      <c r="I191" s="3" t="n"/>
-      <c r="J191" s="3" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>Spiced Cinnamon Apple Spritz</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C192" s="3" t="n">
-        <v>550</v>
-      </c>
-      <c r="D192" s="3" t="n"/>
-      <c r="E192" s="3" t="n"/>
-      <c r="F192" s="3" t="n"/>
-      <c r="G192" s="3" t="n"/>
-      <c r="H192" s="3" t="n"/>
-      <c r="I192" s="3" t="n"/>
-      <c r="J192" s="3" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="3" t="inlineStr">
-        <is>
-          <t>Amaretto Sour</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C193" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D193" s="3" t="n"/>
-      <c r="E193" s="3" t="n"/>
-      <c r="F193" s="3" t="n"/>
-      <c r="G193" s="3" t="n"/>
-      <c r="H193" s="3" t="n"/>
-      <c r="I193" s="3" t="n"/>
-      <c r="J193" s="3" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="3" t="inlineStr">
-        <is>
-          <t>Pinacolada</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C194" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D194" s="3" t="n"/>
-      <c r="E194" s="3" t="n"/>
-      <c r="F194" s="3" t="n"/>
-      <c r="G194" s="3" t="n"/>
-      <c r="H194" s="3" t="n"/>
-      <c r="I194" s="3" t="n"/>
-      <c r="J194" s="3" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="inlineStr">
-        <is>
-          <t>Sex On The Beach</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C195" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D195" s="3" t="n"/>
-      <c r="E195" s="3" t="n"/>
-      <c r="F195" s="3" t="n"/>
-      <c r="G195" s="3" t="n"/>
-      <c r="H195" s="3" t="n"/>
-      <c r="I195" s="3" t="n"/>
-      <c r="J195" s="3" t="n"/>
-    </row>
-    <row r="196"/>
-    <row r="197">
-      <c r="A197" s="1" t="inlineStr">
-        <is>
-          <t>THIS MONTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="198"/>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>Floating Net Sales</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="n"/>
-      <c r="C199" s="2" t="n"/>
-      <c r="D199" s="2" t="n"/>
-      <c r="E199" s="2" t="n"/>
-      <c r="F199" s="2" t="n"/>
-      <c r="G199" s="2" t="n"/>
-      <c r="H199" s="2" t="n"/>
-      <c r="I199" s="2" t="n"/>
-      <c r="J199" s="2" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="3" t="n">
-        <v>207482</v>
-      </c>
-      <c r="B200" s="3" t="n"/>
-      <c r="C200" s="3" t="n"/>
-      <c r="D200" s="3" t="n"/>
-      <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="n"/>
-      <c r="G200" s="3" t="n"/>
-      <c r="H200" s="3" t="n"/>
-      <c r="I200" s="3" t="n"/>
-      <c r="J200" s="3" t="n"/>
-    </row>
-    <row r="201"/>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>Items</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="n"/>
-      <c r="F202" s="2" t="n"/>
-      <c r="G202" s="2" t="n"/>
-      <c r="H202" s="2" t="n"/>
-      <c r="I202" s="2" t="n"/>
-      <c r="J202" s="2" t="n"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="n"/>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>cashier</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="n">
-        <v>207482</v>
-      </c>
-      <c r="D203" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E203" s="3" t="n"/>
-      <c r="F203" s="3" t="n"/>
-      <c r="G203" s="3" t="n"/>
-      <c r="H203" s="3" t="n"/>
-      <c r="I203" s="3" t="n"/>
-      <c r="J203" s="3" t="n"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>Armie Rose Rey</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="n">
-        <v>26540</v>
-      </c>
-      <c r="D204" s="3" t="n">
-        <v>151</v>
-      </c>
-      <c r="E204" s="3" t="n"/>
-      <c r="F204" s="3" t="n"/>
-      <c r="G204" s="3" t="n"/>
-      <c r="H204" s="3" t="n"/>
-      <c r="I204" s="3" t="n"/>
-      <c r="J204" s="3" t="n"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>Rexan Gleem Gaid</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="D205" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E205" s="3" t="n"/>
-      <c r="F205" s="3" t="n"/>
-      <c r="G205" s="3" t="n"/>
-      <c r="H205" s="3" t="n"/>
-      <c r="I205" s="3" t="n"/>
-      <c r="J205" s="3" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="3" t="inlineStr">
-        <is>
-          <t>Cherry Ann Lumactod</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C206" s="3" t="n">
-        <v>7700</v>
-      </c>
-      <c r="D206" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="E206" s="3" t="n"/>
-      <c r="F206" s="3" t="n"/>
-      <c r="G206" s="3" t="n"/>
-      <c r="H206" s="3" t="n"/>
-      <c r="I206" s="3" t="n"/>
-      <c r="J206" s="3" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>Anna Mae Dela Fuente</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="n">
-        <v>20390</v>
-      </c>
-      <c r="D207" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="E207" s="3" t="n"/>
-      <c r="F207" s="3" t="n"/>
-      <c r="G207" s="3" t="n"/>
-      <c r="H207" s="3" t="n"/>
-      <c r="I207" s="3" t="n"/>
-      <c r="J207" s="3" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="3" t="inlineStr">
-        <is>
-          <t>Joey Elijan</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="n">
-        <v>13890</v>
-      </c>
-      <c r="D208" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="E208" s="3" t="n"/>
-      <c r="F208" s="3" t="n"/>
-      <c r="G208" s="3" t="n"/>
-      <c r="H208" s="3" t="n"/>
-      <c r="I208" s="3" t="n"/>
-      <c r="J208" s="3" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>Joraly Angeles</t>
-        </is>
-      </c>
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="n">
-        <v>6500</v>
-      </c>
-      <c r="D209" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="E209" s="3" t="n"/>
-      <c r="F209" s="3" t="n"/>
-      <c r="G209" s="3" t="n"/>
-      <c r="H209" s="3" t="n"/>
-      <c r="I209" s="3" t="n"/>
-      <c r="J209" s="3" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>Kenneth John Mart Jusos</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="n">
-        <v>22310</v>
-      </c>
-      <c r="D210" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="E210" s="3" t="n"/>
-      <c r="F210" s="3" t="n"/>
-      <c r="G210" s="3" t="n"/>
-      <c r="H210" s="3" t="n"/>
-      <c r="I210" s="3" t="n"/>
-      <c r="J210" s="3" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>Krisia Favila</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D211" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E211" s="3" t="n"/>
-      <c r="F211" s="3" t="n"/>
-      <c r="G211" s="3" t="n"/>
-      <c r="H211" s="3" t="n"/>
-      <c r="I211" s="3" t="n"/>
-      <c r="J211" s="3" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="3" t="inlineStr">
-        <is>
-          <t>Daizer Raye Paglicawan</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C212" s="3" t="n">
-        <v>1020</v>
-      </c>
-      <c r="D212" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E212" s="3" t="n"/>
-      <c r="F212" s="3" t="n"/>
-      <c r="G212" s="3" t="n"/>
-      <c r="H212" s="3" t="n"/>
-      <c r="I212" s="3" t="n"/>
-      <c r="J212" s="3" t="n"/>
-    </row>
-    <row r="213"/>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="n"/>
-      <c r="E214" s="2" t="n"/>
-      <c r="F214" s="2" t="n"/>
-      <c r="G214" s="2" t="n"/>
-      <c r="H214" s="2" t="n"/>
-      <c r="I214" s="2" t="n"/>
-      <c r="J214" s="2" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="3" t="inlineStr">
-        <is>
-          <t>Tuna</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C215" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="D215" s="3" t="n"/>
-      <c r="E215" s="3" t="n"/>
-      <c r="F215" s="3" t="n"/>
-      <c r="G215" s="3" t="n"/>
-      <c r="H215" s="3" t="n"/>
-      <c r="I215" s="3" t="n"/>
-      <c r="J215" s="3" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="3" t="inlineStr">
-        <is>
-          <t>Calamares</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C216" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="D216" s="3" t="n"/>
-      <c r="E216" s="3" t="n"/>
-      <c r="F216" s="3" t="n"/>
-      <c r="G216" s="3" t="n"/>
-      <c r="H216" s="3" t="n"/>
-      <c r="I216" s="3" t="n"/>
-      <c r="J216" s="3" t="n"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>Mango</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C217" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D217" s="3" t="n"/>
-      <c r="E217" s="3" t="n"/>
-      <c r="F217" s="3" t="n"/>
-      <c r="G217" s="3" t="n"/>
-      <c r="H217" s="3" t="n"/>
-      <c r="I217" s="3" t="n"/>
-      <c r="J217" s="3" t="n"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>Rice</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C218" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D218" s="3" t="n"/>
-      <c r="E218" s="3" t="n"/>
-      <c r="F218" s="3" t="n"/>
-      <c r="G218" s="3" t="n"/>
-      <c r="H218" s="3" t="n"/>
-      <c r="I218" s="3" t="n"/>
-      <c r="J218" s="3" t="n"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="3" t="inlineStr">
-        <is>
-          <t>KAYAKING</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C219" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="D219" s="3" t="n"/>
-      <c r="E219" s="3" t="n"/>
-      <c r="F219" s="3" t="n"/>
-      <c r="G219" s="3" t="n"/>
-      <c r="H219" s="3" t="n"/>
-      <c r="I219" s="3" t="n"/>
-      <c r="J219" s="3" t="n"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>Smoked Buffalo Wings</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="C220" s="3" t="n">
-        <v>7600</v>
-      </c>
-      <c r="D220" s="3" t="n"/>
-      <c r="E220" s="3" t="n"/>
-      <c r="F220" s="3" t="n"/>
-      <c r="G220" s="3" t="n"/>
-      <c r="H220" s="3" t="n"/>
-      <c r="I220" s="3" t="n"/>
-      <c r="J220" s="3" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>Tropicale</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C221" s="3" t="n">
-        <v>3900</v>
-      </c>
-      <c r="D221" s="3" t="n"/>
-      <c r="E221" s="3" t="n"/>
-      <c r="F221" s="3" t="n"/>
-      <c r="G221" s="3" t="n"/>
-      <c r="H221" s="3" t="n"/>
-      <c r="I221" s="3" t="n"/>
-      <c r="J221" s="3" t="n"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="3" t="inlineStr">
-        <is>
-          <t>Sunset View - C1 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C222" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D222" s="3" t="n"/>
-      <c r="E222" s="3" t="n"/>
-      <c r="F222" s="3" t="n"/>
-      <c r="G222" s="3" t="n"/>
-      <c r="H222" s="3" t="n"/>
-      <c r="I222" s="3" t="n"/>
-      <c r="J222" s="3" t="n"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="3" t="inlineStr">
-        <is>
-          <t>Front Facade - T18 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C223" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D223" s="3" t="n"/>
-      <c r="E223" s="3" t="n"/>
-      <c r="F223" s="3" t="n"/>
-      <c r="G223" s="3" t="n"/>
-      <c r="H223" s="3" t="n"/>
-      <c r="I223" s="3" t="n"/>
-      <c r="J223" s="3" t="n"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="3" t="inlineStr">
-        <is>
-          <t>Front Facade - T19 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C224" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D224" s="3" t="n"/>
-      <c r="E224" s="3" t="n"/>
-      <c r="F224" s="3" t="n"/>
-      <c r="G224" s="3" t="n"/>
-      <c r="H224" s="3" t="n"/>
-      <c r="I224" s="3" t="n"/>
-      <c r="J224" s="3" t="n"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="3" t="inlineStr">
-        <is>
-          <t>Sunset View - C2 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C225" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D225" s="3" t="n"/>
-      <c r="E225" s="3" t="n"/>
-      <c r="F225" s="3" t="n"/>
-      <c r="G225" s="3" t="n"/>
-      <c r="H225" s="3" t="n"/>
-      <c r="I225" s="3" t="n"/>
-      <c r="J225" s="3" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="3" t="inlineStr">
-        <is>
-          <t>Sunset View - C3 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C226" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D226" s="3" t="n"/>
-      <c r="E226" s="3" t="n"/>
-      <c r="F226" s="3" t="n"/>
-      <c r="G226" s="3" t="n"/>
-      <c r="H226" s="3" t="n"/>
-      <c r="I226" s="3" t="n"/>
-      <c r="J226" s="3" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="3" t="inlineStr">
-        <is>
-          <t>Pepperoni</t>
-        </is>
-      </c>
-      <c r="B227" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C227" s="3" t="n">
-        <v>11200</v>
-      </c>
-      <c r="D227" s="3" t="n"/>
-      <c r="E227" s="3" t="n"/>
-      <c r="F227" s="3" t="n"/>
-      <c r="G227" s="3" t="n"/>
-      <c r="H227" s="3" t="n"/>
-      <c r="I227" s="3" t="n"/>
-      <c r="J227" s="3" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="3" t="inlineStr">
-        <is>
-          <t>Wahoo Ceviche</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C228" s="3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D228" s="3" t="n"/>
-      <c r="E228" s="3" t="n"/>
-      <c r="F228" s="3" t="n"/>
-      <c r="G228" s="3" t="n"/>
-      <c r="H228" s="3" t="n"/>
-      <c r="I228" s="3" t="n"/>
-      <c r="J228" s="3" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="3" t="inlineStr">
-        <is>
-          <t>San Mig Light</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="C229" s="3" t="n">
-        <v>4950</v>
-      </c>
-      <c r="D229" s="3" t="n"/>
-      <c r="E229" s="3" t="n"/>
-      <c r="F229" s="3" t="n"/>
-      <c r="G229" s="3" t="n"/>
-      <c r="H229" s="3" t="n"/>
-      <c r="I229" s="3" t="n"/>
-      <c r="J229" s="3" t="n"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="3" t="inlineStr">
-        <is>
-          <t>Sex On The Beach</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C230" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D230" s="3" t="n"/>
-      <c r="E230" s="3" t="n"/>
-      <c r="F230" s="3" t="n"/>
-      <c r="G230" s="3" t="n"/>
-      <c r="H230" s="3" t="n"/>
-      <c r="I230" s="3" t="n"/>
-      <c r="J230" s="3" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="3" t="inlineStr">
-        <is>
-          <t>Fruity Margarita</t>
-        </is>
-      </c>
-      <c r="B231" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="C231" s="3" t="n">
-        <v>5700</v>
-      </c>
-      <c r="D231" s="3" t="n"/>
-      <c r="E231" s="3" t="n"/>
-      <c r="F231" s="3" t="n"/>
-      <c r="G231" s="3" t="n"/>
-      <c r="H231" s="3" t="n"/>
-      <c r="I231" s="3" t="n"/>
-      <c r="J231" s="3" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="3" t="inlineStr">
-        <is>
-          <t>Tuna Crudo</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C232" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D232" s="3" t="n"/>
-      <c r="E232" s="3" t="n"/>
-      <c r="F232" s="3" t="n"/>
-      <c r="G232" s="3" t="n"/>
-      <c r="H232" s="3" t="n"/>
-      <c r="I232" s="3" t="n"/>
-      <c r="J232" s="3" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="3" t="inlineStr">
-        <is>
-          <t>Caipiranha</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C233" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="D233" s="3" t="n"/>
-      <c r="E233" s="3" t="n"/>
-      <c r="F233" s="3" t="n"/>
-      <c r="G233" s="3" t="n"/>
-      <c r="H233" s="3" t="n"/>
-      <c r="I233" s="3" t="n"/>
-      <c r="J233" s="3" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="3" t="inlineStr">
-        <is>
-          <t>Cosmopolitan</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C234" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D234" s="3" t="n"/>
-      <c r="E234" s="3" t="n"/>
-      <c r="F234" s="3" t="n"/>
-      <c r="G234" s="3" t="n"/>
-      <c r="H234" s="3" t="n"/>
-      <c r="I234" s="3" t="n"/>
-      <c r="J234" s="3" t="n"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="3" t="inlineStr">
-        <is>
-          <t>Ragu Alla Bolognese With Parmesan Espuma</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C235" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="D235" s="3" t="n"/>
-      <c r="E235" s="3" t="n"/>
-      <c r="F235" s="3" t="n"/>
-      <c r="G235" s="3" t="n"/>
-      <c r="H235" s="3" t="n"/>
-      <c r="I235" s="3" t="n"/>
-      <c r="J235" s="3" t="n"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="3" t="inlineStr">
-        <is>
-          <t>Ginger-Basil-Cucumber Lemonade</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C236" s="3" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D236" s="3" t="n"/>
-      <c r="E236" s="3" t="n"/>
-      <c r="F236" s="3" t="n"/>
-      <c r="G236" s="3" t="n"/>
-      <c r="H236" s="3" t="n"/>
-      <c r="I236" s="3" t="n"/>
-      <c r="J236" s="3" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="3" t="inlineStr">
-        <is>
-          <t>San Mig Pale Pilsen</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C237" s="3" t="n">
-        <v>8400</v>
-      </c>
-      <c r="D237" s="3" t="n"/>
-      <c r="E237" s="3" t="n"/>
-      <c r="F237" s="3" t="n"/>
-      <c r="G237" s="3" t="n"/>
-      <c r="H237" s="3" t="n"/>
-      <c r="I237" s="3" t="n"/>
-      <c r="J237" s="3" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="3" t="inlineStr">
-        <is>
-          <t>Bottled Water</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="C238" s="3" t="n">
-        <v>2200</v>
-      </c>
-      <c r="D238" s="3" t="n"/>
-      <c r="E238" s="3" t="n"/>
-      <c r="F238" s="3" t="n"/>
-      <c r="G238" s="3" t="n"/>
-      <c r="H238" s="3" t="n"/>
-      <c r="I238" s="3" t="n"/>
-      <c r="J238" s="3" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="3" t="inlineStr">
-        <is>
-          <t>Coke Zero</t>
-        </is>
-      </c>
-      <c r="B239" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C239" s="3" t="n">
-        <v>840</v>
-      </c>
-      <c r="D239" s="3" t="n"/>
-      <c r="E239" s="3" t="n"/>
-      <c r="F239" s="3" t="n"/>
-      <c r="G239" s="3" t="n"/>
-      <c r="H239" s="3" t="n"/>
-      <c r="I239" s="3" t="n"/>
-      <c r="J239" s="3" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="3" t="inlineStr">
-        <is>
-          <t>Cafe Latte</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C240" s="3" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D240" s="3" t="n"/>
-      <c r="E240" s="3" t="n"/>
-      <c r="F240" s="3" t="n"/>
-      <c r="G240" s="3" t="n"/>
-      <c r="H240" s="3" t="n"/>
-      <c r="I240" s="3" t="n"/>
-      <c r="J240" s="3" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="3" t="inlineStr">
-        <is>
-          <t>Carbonara Oceanica</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C241" s="3" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D241" s="3" t="n"/>
-      <c r="E241" s="3" t="n"/>
-      <c r="F241" s="3" t="n"/>
-      <c r="G241" s="3" t="n"/>
-      <c r="H241" s="3" t="n"/>
-      <c r="I241" s="3" t="n"/>
-      <c r="J241" s="3" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="3" t="inlineStr">
-        <is>
-          <t>Sprite</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C242" s="3" t="n">
-        <v>1080</v>
-      </c>
-      <c r="D242" s="3" t="n"/>
-      <c r="E242" s="3" t="n"/>
-      <c r="F242" s="3" t="n"/>
-      <c r="G242" s="3" t="n"/>
-      <c r="H242" s="3" t="n"/>
-      <c r="I242" s="3" t="n"/>
-      <c r="J242" s="3" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="3" t="inlineStr">
-        <is>
-          <t>Margherita</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C243" s="3" t="n">
-        <v>4800</v>
-      </c>
-      <c r="D243" s="3" t="n"/>
-      <c r="E243" s="3" t="n"/>
-      <c r="F243" s="3" t="n"/>
-      <c r="G243" s="3" t="n"/>
-      <c r="H243" s="3" t="n"/>
-      <c r="I243" s="3" t="n"/>
-      <c r="J243" s="3" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="3" t="inlineStr">
-        <is>
-          <t>San Mig Pure Malt</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C244" s="3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D244" s="3" t="n"/>
-      <c r="E244" s="3" t="n"/>
-      <c r="F244" s="3" t="n"/>
-      <c r="G244" s="3" t="n"/>
-      <c r="H244" s="3" t="n"/>
-      <c r="I244" s="3" t="n"/>
-      <c r="J244" s="3" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="3" t="inlineStr">
-        <is>
-          <t>MAI TAI WD</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="C245" s="3" t="n">
-        <v>12250</v>
-      </c>
-      <c r="D245" s="3" t="n"/>
-      <c r="E245" s="3" t="n"/>
-      <c r="F245" s="3" t="n"/>
-      <c r="G245" s="3" t="n"/>
-      <c r="H245" s="3" t="n"/>
-      <c r="I245" s="3" t="n"/>
-      <c r="J245" s="3" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="3" t="inlineStr">
-        <is>
-          <t>Buffet</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="C246" s="3" t="n">
-        <v>55500</v>
-      </c>
-      <c r="D246" s="3" t="n"/>
-      <c r="E246" s="3" t="n"/>
-      <c r="F246" s="3" t="n"/>
-      <c r="G246" s="3" t="n"/>
-      <c r="H246" s="3" t="n"/>
-      <c r="I246" s="3" t="n"/>
-      <c r="J246" s="3" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="3" t="inlineStr">
-        <is>
-          <t>Jacuzzi Couch - C4 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C247" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D247" s="3" t="n"/>
-      <c r="E247" s="3" t="n"/>
-      <c r="F247" s="3" t="n"/>
-      <c r="G247" s="3" t="n"/>
-      <c r="H247" s="3" t="n"/>
-      <c r="I247" s="3" t="n"/>
-      <c r="J247" s="3" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="3" t="inlineStr">
-        <is>
-          <t>Jacuzzi Couch - C7 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D248" s="3" t="n"/>
-      <c r="E248" s="3" t="n"/>
-      <c r="F248" s="3" t="n"/>
-      <c r="G248" s="3" t="n"/>
-      <c r="H248" s="3" t="n"/>
-      <c r="I248" s="3" t="n"/>
-      <c r="J248" s="3" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="3" t="inlineStr">
-        <is>
-          <t>Prawn Croquettes</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C249" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D249" s="3" t="n"/>
-      <c r="E249" s="3" t="n"/>
-      <c r="F249" s="3" t="n"/>
-      <c r="G249" s="3" t="n"/>
-      <c r="H249" s="3" t="n"/>
-      <c r="I249" s="3" t="n"/>
-      <c r="J249" s="3" t="n"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="3" t="inlineStr">
-        <is>
-          <t>Marina Verde Lasagna</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C250" s="3" t="n">
-        <v>1340</v>
-      </c>
-      <c r="D250" s="3" t="n"/>
-      <c r="E250" s="3" t="n"/>
-      <c r="F250" s="3" t="n"/>
-      <c r="G250" s="3" t="n"/>
-      <c r="H250" s="3" t="n"/>
-      <c r="I250" s="3" t="n"/>
-      <c r="J250" s="3" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="3" t="inlineStr">
-        <is>
-          <t>Cafe Mocha</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C251" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D251" s="3" t="n"/>
-      <c r="E251" s="3" t="n"/>
-      <c r="F251" s="3" t="n"/>
-      <c r="G251" s="3" t="n"/>
-      <c r="H251" s="3" t="n"/>
-      <c r="I251" s="3" t="n"/>
-      <c r="J251" s="3" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="3" t="inlineStr">
-        <is>
-          <t>Front Facade - T1 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C252" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D252" s="3" t="n"/>
-      <c r="E252" s="3" t="n"/>
-      <c r="F252" s="3" t="n"/>
-      <c r="G252" s="3" t="n"/>
-      <c r="H252" s="3" t="n"/>
-      <c r="I252" s="3" t="n"/>
-      <c r="J252" s="3" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="3" t="inlineStr">
-        <is>
-          <t>Daiquiri</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C253" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D253" s="3" t="n"/>
-      <c r="E253" s="3" t="n"/>
-      <c r="F253" s="3" t="n"/>
-      <c r="G253" s="3" t="n"/>
-      <c r="H253" s="3" t="n"/>
-      <c r="I253" s="3" t="n"/>
-      <c r="J253" s="3" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="3" t="inlineStr">
-        <is>
-          <t>Fruity Daiqueri</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C254" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D254" s="3" t="n"/>
-      <c r="E254" s="3" t="n"/>
-      <c r="F254" s="3" t="n"/>
-      <c r="G254" s="3" t="n"/>
-      <c r="H254" s="3" t="n"/>
-      <c r="I254" s="3" t="n"/>
-      <c r="J254" s="3" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="3" t="inlineStr">
-        <is>
-          <t>JOSE CUERVO GOLD 1Lt.</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C255" s="3" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D255" s="3" t="n"/>
-      <c r="E255" s="3" t="n"/>
-      <c r="F255" s="3" t="n"/>
-      <c r="G255" s="3" t="n"/>
-      <c r="H255" s="3" t="n"/>
-      <c r="I255" s="3" t="n"/>
-      <c r="J255" s="3" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="3" t="inlineStr">
-        <is>
-          <t>San Mig Apple</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C256" s="3" t="n">
-        <v>450</v>
-      </c>
-      <c r="D256" s="3" t="n"/>
-      <c r="E256" s="3" t="n"/>
-      <c r="F256" s="3" t="n"/>
-      <c r="G256" s="3" t="n"/>
-      <c r="H256" s="3" t="n"/>
-      <c r="I256" s="3" t="n"/>
-      <c r="J256" s="3" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="3" t="inlineStr">
-        <is>
-          <t>Angus Ribeye</t>
-        </is>
-      </c>
-      <c r="B257" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C257" s="3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D257" s="3" t="n"/>
-      <c r="E257" s="3" t="n"/>
-      <c r="F257" s="3" t="n"/>
-      <c r="G257" s="3" t="n"/>
-      <c r="H257" s="3" t="n"/>
-      <c r="I257" s="3" t="n"/>
-      <c r="J257" s="3" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="3" t="inlineStr">
-        <is>
-          <t>Espresso</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C258" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D258" s="3" t="n"/>
-      <c r="E258" s="3" t="n"/>
-      <c r="F258" s="3" t="n"/>
-      <c r="G258" s="3" t="n"/>
-      <c r="H258" s="3" t="n"/>
-      <c r="I258" s="3" t="n"/>
-      <c r="J258" s="3" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="3" t="inlineStr">
-        <is>
-          <t>JACK DANIELS Per Shot</t>
-        </is>
-      </c>
-      <c r="B259" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C259" s="3" t="n">
-        <v>700</v>
-      </c>
-      <c r="D259" s="3" t="n"/>
-      <c r="E259" s="3" t="n"/>
-      <c r="F259" s="3" t="n"/>
-      <c r="G259" s="3" t="n"/>
-      <c r="H259" s="3" t="n"/>
-      <c r="I259" s="3" t="n"/>
-      <c r="J259" s="3" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="3" t="inlineStr">
-        <is>
-          <t>Mango Lemonade</t>
-        </is>
-      </c>
-      <c r="B260" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C260" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D260" s="3" t="n"/>
-      <c r="E260" s="3" t="n"/>
-      <c r="F260" s="3" t="n"/>
-      <c r="G260" s="3" t="n"/>
-      <c r="H260" s="3" t="n"/>
-      <c r="I260" s="3" t="n"/>
-      <c r="J260" s="3" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="3" t="inlineStr">
-        <is>
-          <t>MAI TAI N/A</t>
-        </is>
-      </c>
-      <c r="B261" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="C261" s="3" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D261" s="3" t="n"/>
-      <c r="E261" s="3" t="n"/>
-      <c r="F261" s="3" t="n"/>
-      <c r="G261" s="3" t="n"/>
-      <c r="H261" s="3" t="n"/>
-      <c r="I261" s="3" t="n"/>
-      <c r="J261" s="3" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="3" t="inlineStr">
-        <is>
-          <t>Blue Ocean Mule</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C262" s="3" t="n">
-        <v>4950</v>
-      </c>
-      <c r="D262" s="3" t="n"/>
-      <c r="E262" s="3" t="n"/>
-      <c r="F262" s="3" t="n"/>
-      <c r="G262" s="3" t="n"/>
-      <c r="H262" s="3" t="n"/>
-      <c r="I262" s="3" t="n"/>
-      <c r="J262" s="3" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="3" t="inlineStr">
-        <is>
-          <t>Pinacolada</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C263" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D263" s="3" t="n"/>
-      <c r="E263" s="3" t="n"/>
-      <c r="F263" s="3" t="n"/>
-      <c r="G263" s="3" t="n"/>
-      <c r="H263" s="3" t="n"/>
-      <c r="I263" s="3" t="n"/>
-      <c r="J263" s="3" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="inlineStr">
-        <is>
-          <t>Coke Regular</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C264" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="D264" s="3" t="n"/>
-      <c r="E264" s="3" t="n"/>
-      <c r="F264" s="3" t="n"/>
-      <c r="G264" s="3" t="n"/>
-      <c r="H264" s="3" t="n"/>
-      <c r="I264" s="3" t="n"/>
-      <c r="J264" s="3" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t>Day Access</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C265" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D265" s="3" t="n"/>
-      <c r="E265" s="3" t="n"/>
-      <c r="F265" s="3" t="n"/>
-      <c r="G265" s="3" t="n"/>
-      <c r="H265" s="3" t="n"/>
-      <c r="I265" s="3" t="n"/>
-      <c r="J265" s="3" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>Amaretto Sour</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C266" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="D266" s="3" t="n"/>
-      <c r="E266" s="3" t="n"/>
-      <c r="F266" s="3" t="n"/>
-      <c r="G266" s="3" t="n"/>
-      <c r="H266" s="3" t="n"/>
-      <c r="I266" s="3" t="n"/>
-      <c r="J266" s="3" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>Surf &amp; Turf Burger</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C267" s="3" t="n">
-        <v>5360</v>
-      </c>
-      <c r="D267" s="3" t="n"/>
-      <c r="E267" s="3" t="n"/>
-      <c r="F267" s="3" t="n"/>
-      <c r="G267" s="3" t="n"/>
-      <c r="H267" s="3" t="n"/>
-      <c r="I267" s="3" t="n"/>
-      <c r="J267" s="3" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Towel </t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C268" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="D268" s="3" t="n"/>
-      <c r="E268" s="3" t="n"/>
-      <c r="F268" s="3" t="n"/>
-      <c r="G268" s="3" t="n"/>
-      <c r="H268" s="3" t="n"/>
-      <c r="I268" s="3" t="n"/>
-      <c r="J268" s="3" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C269" s="3" t="n">
-        <v>750</v>
-      </c>
-      <c r="D269" s="3" t="n"/>
-      <c r="E269" s="3" t="n"/>
-      <c r="F269" s="3" t="n"/>
-      <c r="G269" s="3" t="n"/>
-      <c r="H269" s="3" t="n"/>
-      <c r="I269" s="3" t="n"/>
-      <c r="J269" s="3" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>Pineapple</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C270" s="3" t="n">
-        <v>1250</v>
-      </c>
-      <c r="D270" s="3" t="n"/>
-      <c r="E270" s="3" t="n"/>
-      <c r="F270" s="3" t="n"/>
-      <c r="G270" s="3" t="n"/>
-      <c r="H270" s="3" t="n"/>
-      <c r="I270" s="3" t="n"/>
-      <c r="J270" s="3" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr">
-        <is>
-          <t>MATUA SAUV. BLANC HOUSE WINE</t>
-        </is>
-      </c>
-      <c r="B271" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C271" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D271" s="3" t="n"/>
-      <c r="E271" s="3" t="n"/>
-      <c r="F271" s="3" t="n"/>
-      <c r="G271" s="3" t="n"/>
-      <c r="H271" s="3" t="n"/>
-      <c r="I271" s="3" t="n"/>
-      <c r="J271" s="3" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
-        <is>
-          <t>Port Barton Sunset</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C272" s="3" t="n">
-        <v>2200</v>
-      </c>
-      <c r="D272" s="3" t="n"/>
-      <c r="E272" s="3" t="n"/>
-      <c r="F272" s="3" t="n"/>
-      <c r="G272" s="3" t="n"/>
-      <c r="H272" s="3" t="n"/>
-      <c r="I272" s="3" t="n"/>
-      <c r="J272" s="3" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>Margarita</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C273" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D273" s="3" t="n"/>
-      <c r="E273" s="3" t="n"/>
-      <c r="F273" s="3" t="n"/>
-      <c r="G273" s="3" t="n"/>
-      <c r="H273" s="3" t="n"/>
-      <c r="I273" s="3" t="n"/>
-      <c r="J273" s="3" t="n"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t>Spiced Cinnamon Apple Spritz</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C274" s="3" t="n">
-        <v>2200</v>
-      </c>
-      <c r="D274" s="3" t="n"/>
-      <c r="E274" s="3" t="n"/>
-      <c r="F274" s="3" t="n"/>
-      <c r="G274" s="3" t="n"/>
-      <c r="H274" s="3" t="n"/>
-      <c r="I274" s="3" t="n"/>
-      <c r="J274" s="3" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="3" t="inlineStr">
-        <is>
-          <t>Coconut Mousse</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C275" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D275" s="3" t="n"/>
-      <c r="E275" s="3" t="n"/>
-      <c r="F275" s="3" t="n"/>
-      <c r="G275" s="3" t="n"/>
-      <c r="H275" s="3" t="n"/>
-      <c r="I275" s="3" t="n"/>
-      <c r="J275" s="3" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t>Sambuka</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C276" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="D276" s="3" t="n"/>
-      <c r="E276" s="3" t="n"/>
-      <c r="F276" s="3" t="n"/>
-      <c r="G276" s="3" t="n"/>
-      <c r="H276" s="3" t="n"/>
-      <c r="I276" s="3" t="n"/>
-      <c r="J276" s="3" t="n"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="3" t="inlineStr">
-        <is>
-          <t>SHOT JOSE CUERVO GOLD</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C277" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="D277" s="3" t="n"/>
-      <c r="E277" s="3" t="n"/>
-      <c r="F277" s="3" t="n"/>
-      <c r="G277" s="3" t="n"/>
-      <c r="H277" s="3" t="n"/>
-      <c r="I277" s="3" t="n"/>
-      <c r="J277" s="3" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="3" t="inlineStr">
-        <is>
-          <t>Cappuccino</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C278" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="D278" s="3" t="n"/>
-      <c r="E278" s="3" t="n"/>
-      <c r="F278" s="3" t="n"/>
-      <c r="G278" s="3" t="n"/>
-      <c r="H278" s="3" t="n"/>
-      <c r="I278" s="3" t="n"/>
-      <c r="J278" s="3" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="3" t="inlineStr">
-        <is>
-          <t>Estrella Galicia</t>
-        </is>
-      </c>
-      <c r="B279" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C279" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="D279" s="3" t="n"/>
-      <c r="E279" s="3" t="n"/>
-      <c r="F279" s="3" t="n"/>
-      <c r="G279" s="3" t="n"/>
-      <c r="H279" s="3" t="n"/>
-      <c r="I279" s="3" t="n"/>
-      <c r="J279" s="3" t="n"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="3" t="inlineStr">
-        <is>
-          <t>HAWAIIAN</t>
-        </is>
-      </c>
-      <c r="B280" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C280" s="3" t="n">
-        <v>650</v>
-      </c>
-      <c r="D280" s="3" t="n"/>
-      <c r="E280" s="3" t="n"/>
-      <c r="F280" s="3" t="n"/>
-      <c r="G280" s="3" t="n"/>
-      <c r="H280" s="3" t="n"/>
-      <c r="I280" s="3" t="n"/>
-      <c r="J280" s="3" t="n"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="3" t="inlineStr">
-        <is>
-          <t>Front Facade - T4 - Main Deck</t>
-        </is>
-      </c>
-      <c r="B281" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C281" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D281" s="3" t="n"/>
-      <c r="E281" s="3" t="n"/>
-      <c r="F281" s="3" t="n"/>
-      <c r="G281" s="3" t="n"/>
-      <c r="H281" s="3" t="n"/>
-      <c r="I281" s="3" t="n"/>
-      <c r="J281" s="3" t="n"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="3" t="inlineStr">
-        <is>
-          <t>BOTTLED WATER 500 ML</t>
-        </is>
-      </c>
-      <c r="B282" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C282" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D282" s="3" t="n"/>
-      <c r="E282" s="3" t="n"/>
-      <c r="F282" s="3" t="n"/>
-      <c r="G282" s="3" t="n"/>
-      <c r="H282" s="3" t="n"/>
-      <c r="I282" s="3" t="n"/>
-      <c r="J282" s="3" t="n"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="3" t="inlineStr">
-        <is>
-          <t>TANDUAY RUM</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C283" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="D283" s="3" t="n"/>
-      <c r="E283" s="3" t="n"/>
-      <c r="F283" s="3" t="n"/>
-      <c r="G283" s="3" t="n"/>
-      <c r="H283" s="3" t="n"/>
-      <c r="I283" s="3" t="n"/>
-      <c r="J283" s="3" t="n"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="3" t="inlineStr">
-        <is>
-          <t>COKE REGULAR</t>
-        </is>
-      </c>
-      <c r="B284" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C284" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="D284" s="3" t="n"/>
-      <c r="E284" s="3" t="n"/>
-      <c r="F284" s="3" t="n"/>
-      <c r="G284" s="3" t="n"/>
-      <c r="H284" s="3" t="n"/>
-      <c r="I284" s="3" t="n"/>
-      <c r="J284" s="3" t="n"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="3" t="inlineStr">
-        <is>
-          <t>TANQUERAY Per Shot</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C285" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="D285" s="3" t="n"/>
-      <c r="E285" s="3" t="n"/>
-      <c r="F285" s="3" t="n"/>
-      <c r="G285" s="3" t="n"/>
-      <c r="H285" s="3" t="n"/>
-      <c r="I285" s="3" t="n"/>
-      <c r="J285" s="3" t="n"/>
+      <c r="K155" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A197:J197"/>
-    <mergeCell ref="A105:J105"/>
-    <mergeCell ref="A114:J114"/>
-    <mergeCell ref="A152:J152"/>
+    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A140:K140"/>
+    <mergeCell ref="A112:K112"/>
+    <mergeCell ref="A125:K125"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dashboard_report.xlsx
+++ b/dashboard_report.xlsx
@@ -452,10 +452,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:K285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -832,7 +832,7 @@
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Elaine Dela Cruz, Anna Mae Dela Fuente, Cashier</t>
+          <t>Anna Mae Dela Fuente, Elaine Dela Cruz, Cashier</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -879,7 +879,7 @@
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Elaine Dela Cruz, Cashier</t>
+          <t>Cashier, Elaine Dela Cruz</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -926,7 +926,7 @@
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Elaine Dela Cruz, Cashier</t>
+          <t>Cashier, Elaine Dela Cruz</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -973,7 +973,7 @@
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Dimee Dela Cruz, Armie Rose Rey, Cherry Ann Lumactod</t>
+          <t>Cherry Ann Lumactod, Dimee Dela Cruz, Armie Rose Rey</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1020,7 +1020,7 @@
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey, Anna Mae Dela Fuente, Cashier</t>
+          <t>Anna Mae Dela Fuente, Armie Rose Rey, Cashier</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1161,7 +1161,7 @@
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey, Cherry Ann Lumactod</t>
+          <t>Cherry Ann Lumactod, Armie Rose Rey</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey, Cherry Ann Lumactod, Cashier</t>
+          <t>Cherry Ann Lumactod, Cashier, Armie Rose Rey</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1302,7 +1302,7 @@
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey, Cherry Ann Lumactod</t>
+          <t>Cherry Ann Lumactod, Armie Rose Rey</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1396,7 +1396,7 @@
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Joraly Angeles, Armie Rose Rey</t>
+          <t>Armie Rose Rey, Joraly Angeles</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Elaine Dela Cruz, Cashier</t>
+          <t>Cashier, Elaine Dela Cruz</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Elaine Dela Cruz, Mellan Joy Lapidez</t>
+          <t>Mellan Joy Lapidez, Elaine Dela Cruz</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1584,7 +1584,7 @@
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey, Cherry Ann Lumactod, Rexan Gleem Gaid</t>
+          <t>Cherry Ann Lumactod, Armie Rose Rey, Rexan Gleem Gaid</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1678,7 +1678,7 @@
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey, Anna Mae Dela Fuente, Joey Elijan, Rexan Gleem Gaid</t>
+          <t>Anna Mae Dela Fuente, Armie Rose Rey, Joey Elijan, Rexan Gleem Gaid</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1772,7 +1772,7 @@
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Joraly Angeles, Kenneth John Mart Jusos, Cherry Ann Lumactod, Joey Elijan</t>
+          <t>Cherry Ann Lumactod, Joey Elijan, Joraly Angeles, Kenneth John Mart Jusos</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1819,7 +1819,7 @@
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Kenneth John Mart Jusos, Rexan Gleem Gaid, Armie Rose Rey, Anna Mae Dela Fuente, Joey Elijan</t>
+          <t>Anna Mae Dela Fuente, Rexan Gleem Gaid, Joey Elijan, Kenneth John Mart Jusos, Armie Rose Rey</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -2621,7 +2621,7 @@
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Kenneth John Mart Jusos, Cherry Ann Lumactod</t>
+          <t>Cherry Ann Lumactod, Kenneth John Mart Jusos</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2762,7 +2762,7 @@
       <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Anna Mae Dela Fuente, Krisia Favila</t>
+          <t>Krisia Favila, Anna Mae Dela Fuente</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2903,7 +2903,7 @@
       <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey, Anna Mae Dela Fuente</t>
+          <t>Anna Mae Dela Fuente, Armie Rose Rey</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -3185,7 +3185,7 @@
       <c r="D61" s="3" t="n"/>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Joraly Angeles, Krisia Favila</t>
+          <t>Krisia Favila, Joraly Angeles</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3326,7 +3326,7 @@
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey, Anna Mae Dela Fuente, Krisia Favila</t>
+          <t>Krisia Favila, Anna Mae Dela Fuente, Armie Rose Rey</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -4038,7 +4038,7 @@
       <c r="D80" s="3" t="n"/>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Kenneth John Mart Jusos, Krisia Favila</t>
+          <t>Krisia Favila, Kenneth John Mart Jusos</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -5176,143 +5176,119 @@
     </row>
     <row r="111"/>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>YESTERDAY</t>
-        </is>
-      </c>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Item Sold</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+      <c r="J112" s="2" t="n"/>
+      <c r="K112" s="2" t="n"/>
     </row>
     <row r="113"/>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>YESTERDAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="115"/>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Floating Net Sales</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Total Discount</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="n"/>
-      <c r="G114" s="2" t="n"/>
-      <c r="H114" s="2" t="n"/>
-      <c r="I114" s="2" t="n"/>
-      <c r="J114" s="2" t="n"/>
-      <c r="K114" s="2" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="n"/>
+      <c r="H116" s="2" t="n"/>
+      <c r="I116" s="2" t="n"/>
+      <c r="J116" s="2" t="n"/>
+      <c r="K116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
         <v>15125</v>
       </c>
-      <c r="B115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="3" t="n"/>
-      <c r="D115" s="3" t="n"/>
-      <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n"/>
-      <c r="G115" s="3" t="n"/>
-      <c r="H115" s="3" t="n"/>
-      <c r="I115" s="3" t="n"/>
-      <c r="J115" s="3" t="n"/>
-      <c r="K115" s="3" t="n"/>
-    </row>
-    <row r="116"/>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n"/>
+      <c r="D117" s="3" t="n"/>
+      <c r="E117" s="3" t="n"/>
+      <c r="F117" s="3" t="n"/>
+      <c r="G117" s="3" t="n"/>
+      <c r="H117" s="3" t="n"/>
+      <c r="I117" s="3" t="n"/>
+      <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="n"/>
+    </row>
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Items</t>
         </is>
       </c>
-      <c r="E117" s="2" t="n"/>
-      <c r="F117" s="2" t="n"/>
-      <c r="G117" s="2" t="n"/>
-      <c r="H117" s="2" t="n"/>
-      <c r="I117" s="2" t="n"/>
-      <c r="J117" s="2" t="n"/>
-      <c r="K117" s="2" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="n"/>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="n"/>
+      <c r="K119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n"/>
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>cashier</t>
         </is>
       </c>
-      <c r="C118" s="3" t="n">
+      <c r="C120" s="3" t="n">
         <v>15125</v>
       </c>
-      <c r="D118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n"/>
-      <c r="G118" s="3" t="n"/>
-      <c r="H118" s="3" t="n"/>
-      <c r="I118" s="3" t="n"/>
-      <c r="J118" s="3" t="n"/>
-      <c r="K118" s="3" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>Anna Mae Dela Fuente</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>3150</v>
-      </c>
-      <c r="D119" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E119" s="3" t="n"/>
-      <c r="F119" s="3" t="n"/>
-      <c r="G119" s="3" t="n"/>
-      <c r="H119" s="3" t="n"/>
-      <c r="I119" s="3" t="n"/>
-      <c r="J119" s="3" t="n"/>
-      <c r="K119" s="3" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>Joey Elijan</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>1540</v>
-      </c>
       <c r="D120" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E120" s="3" t="n"/>
       <c r="F120" s="3" t="n"/>
@@ -5325,7 +5301,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey</t>
+          <t>Anna Mae Dela Fuente</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -5334,10 +5310,10 @@
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>3050</v>
+        <v>3150</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n"/>
@@ -5350,7 +5326,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Daizer Raye Paglicawan</t>
+          <t>Joey Elijan</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5359,7 +5335,7 @@
         </is>
       </c>
       <c r="C122" s="3" t="n">
-        <v>1020</v>
+        <v>1540</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>4</v>
@@ -5375,7 +5351,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Joraly Angeles</t>
+          <t>Armie Rose Rey</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -5384,10 +5360,10 @@
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>4750</v>
+        <v>3050</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E123" s="3" t="n"/>
       <c r="F123" s="3" t="n"/>
@@ -5397,27 +5373,73 @@
       <c r="J123" s="3" t="n"/>
       <c r="K123" s="3" t="n"/>
     </row>
-    <row r="124"/>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Daizer Raye Paglicawan</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E124" s="3" t="n"/>
+      <c r="F124" s="3" t="n"/>
+      <c r="G124" s="3" t="n"/>
+      <c r="H124" s="3" t="n"/>
+      <c r="I124" s="3" t="n"/>
+      <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="n"/>
+    </row>
     <row r="125">
-      <c r="A125" s="1" t="inlineStr">
-        <is>
-          <t>THIS WEEK</t>
-        </is>
-      </c>
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Joraly Angeles</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>4750</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E125" s="3" t="n"/>
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="3" t="n"/>
+      <c r="H125" s="3" t="n"/>
+      <c r="I125" s="3" t="n"/>
+      <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="n"/>
     </row>
     <row r="126"/>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Floating Net Sales</t>
+          <t>Item Sold</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Total Discount</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n"/>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" s="2" t="n"/>
       <c r="F127" s="2" t="n"/>
@@ -5428,13 +5450,17 @@
       <c r="K127" s="2" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
-        <v>17072</v>
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Tuna Crudo</t>
+        </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>500</v>
+      </c>
       <c r="D128" s="3" t="n"/>
       <c r="E128" s="3" t="n"/>
       <c r="F128" s="3" t="n"/>
@@ -5444,49 +5470,61 @@
       <c r="J128" s="3" t="n"/>
       <c r="K128" s="3" t="n"/>
     </row>
-    <row r="129"/>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Prawn Croquettes</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D129" s="3" t="n"/>
+      <c r="E129" s="3" t="n"/>
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="3" t="n"/>
+      <c r="H129" s="3" t="n"/>
+      <c r="I129" s="3" t="n"/>
+      <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="n"/>
+    </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Items</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="n"/>
-      <c r="F130" s="2" t="n"/>
-      <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2" t="n"/>
-      <c r="I130" s="2" t="n"/>
-      <c r="J130" s="2" t="n"/>
-      <c r="K130" s="2" t="n"/>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Ginger-Basil-Cucumber Lemonade</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
+      <c r="I130" s="3" t="n"/>
+      <c r="J130" s="3" t="n"/>
+      <c r="K130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n"/>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>cashier</t>
-        </is>
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>BOTTLED WATER 500 ML</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C131" s="3" t="n">
-        <v>17072</v>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D131" s="3" t="n"/>
       <c r="E131" s="3" t="n"/>
       <c r="F131" s="3" t="n"/>
       <c r="G131" s="3" t="n"/>
@@ -5498,20 +5536,16 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>Krisia Favila</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>Tropicale</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>1300</v>
+      </c>
+      <c r="D132" s="3" t="n"/>
       <c r="E132" s="3" t="n"/>
       <c r="F132" s="3" t="n"/>
       <c r="G132" s="3" t="n"/>
@@ -5523,20 +5557,16 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Kenneth John Mart Jusos</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>Pineapple</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C133" s="3" t="n">
-        <v>1770</v>
-      </c>
-      <c r="D133" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="D133" s="3" t="n"/>
       <c r="E133" s="3" t="n"/>
       <c r="F133" s="3" t="n"/>
       <c r="G133" s="3" t="n"/>
@@ -5548,20 +5578,16 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>Anna Mae Dela Fuente</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>Cafe Latte</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>3150</v>
-      </c>
-      <c r="D134" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="D134" s="3" t="n"/>
       <c r="E134" s="3" t="n"/>
       <c r="F134" s="3" t="n"/>
       <c r="G134" s="3" t="n"/>
@@ -5573,20 +5599,16 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Joey Elijan</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>San Mig Pale Pilsen</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>1540</v>
-      </c>
-      <c r="D135" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D135" s="3" t="n"/>
       <c r="E135" s="3" t="n"/>
       <c r="F135" s="3" t="n"/>
       <c r="G135" s="3" t="n"/>
@@ -5598,20 +5620,16 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>Margherita</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C136" s="3" t="n">
-        <v>3050</v>
-      </c>
-      <c r="D136" s="3" t="n">
-        <v>7</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="D136" s="3" t="n"/>
       <c r="E136" s="3" t="n"/>
       <c r="F136" s="3" t="n"/>
       <c r="G136" s="3" t="n"/>
@@ -5623,20 +5641,16 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Daizer Raye Paglicawan</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>Blue Ocean Mule</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="C137" s="3" t="n">
-        <v>1020</v>
-      </c>
-      <c r="D137" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>2750</v>
+      </c>
+      <c r="D137" s="3" t="n"/>
       <c r="E137" s="3" t="n"/>
       <c r="F137" s="3" t="n"/>
       <c r="G137" s="3" t="n"/>
@@ -5648,20 +5662,16 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>Joraly Angeles</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>TANDUAY RUM</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C138" s="3" t="n">
-        <v>4750</v>
-      </c>
-      <c r="D138" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="D138" s="3" t="n"/>
       <c r="E138" s="3" t="n"/>
       <c r="F138" s="3" t="n"/>
       <c r="G138" s="3" t="n"/>
@@ -5670,44 +5680,102 @@
       <c r="J138" s="3" t="n"/>
       <c r="K138" s="3" t="n"/>
     </row>
-    <row r="139"/>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>COKE REGULAR</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="D139" s="3" t="n"/>
+      <c r="E139" s="3" t="n"/>
+      <c r="F139" s="3" t="n"/>
+      <c r="G139" s="3" t="n"/>
+      <c r="H139" s="3" t="n"/>
+      <c r="I139" s="3" t="n"/>
+      <c r="J139" s="3" t="n"/>
+      <c r="K139" s="3" t="n"/>
+    </row>
     <row r="140">
-      <c r="A140" s="1" t="inlineStr">
-        <is>
-          <t>THIS MONTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="141"/>
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Surf &amp; Turf Burger</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>670</v>
+      </c>
+      <c r="D140" s="3" t="n"/>
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="3" t="n"/>
+      <c r="G140" s="3" t="n"/>
+      <c r="H140" s="3" t="n"/>
+      <c r="I140" s="3" t="n"/>
+      <c r="J140" s="3" t="n"/>
+      <c r="K140" s="3" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Coke Zero</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D141" s="3" t="n"/>
+      <c r="E141" s="3" t="n"/>
+      <c r="F141" s="3" t="n"/>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
+      <c r="I141" s="3" t="n"/>
+      <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="n"/>
+    </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Floating Net Sales</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Total Discount</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" s="2" t="n"/>
-      <c r="F142" s="2" t="n"/>
-      <c r="G142" s="2" t="n"/>
-      <c r="H142" s="2" t="n"/>
-      <c r="I142" s="2" t="n"/>
-      <c r="J142" s="2" t="n"/>
-      <c r="K142" s="2" t="n"/>
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>San Mig Apple</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D142" s="3" t="n"/>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
+      <c r="I142" s="3" t="n"/>
+      <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n">
-        <v>207482</v>
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Smoked Buffalo Wings</t>
+        </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>400</v>
+      </c>
       <c r="D143" s="3" t="n"/>
       <c r="E143" s="3" t="n"/>
       <c r="F143" s="3" t="n"/>
@@ -5717,49 +5785,61 @@
       <c r="J143" s="3" t="n"/>
       <c r="K143" s="3" t="n"/>
     </row>
-    <row r="144"/>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Pepperoni</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D144" s="3" t="n"/>
+      <c r="E144" s="3" t="n"/>
+      <c r="F144" s="3" t="n"/>
+      <c r="G144" s="3" t="n"/>
+      <c r="H144" s="3" t="n"/>
+      <c r="I144" s="3" t="n"/>
+      <c r="J144" s="3" t="n"/>
+      <c r="K144" s="3" t="n"/>
+    </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Items</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="n"/>
-      <c r="F145" s="2" t="n"/>
-      <c r="G145" s="2" t="n"/>
-      <c r="H145" s="2" t="n"/>
-      <c r="I145" s="2" t="n"/>
-      <c r="J145" s="2" t="n"/>
-      <c r="K145" s="2" t="n"/>
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>TANQUERAY Per Shot</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="D145" s="3" t="n"/>
+      <c r="E145" s="3" t="n"/>
+      <c r="F145" s="3" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="3" t="n"/>
+      <c r="I145" s="3" t="n"/>
+      <c r="J145" s="3" t="n"/>
+      <c r="K145" s="3" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n"/>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>cashier</t>
-        </is>
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Spiced Cinnamon Apple Spritz</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C146" s="3" t="n">
-        <v>207482</v>
-      </c>
-      <c r="D146" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="D146" s="3" t="n"/>
       <c r="E146" s="3" t="n"/>
       <c r="F146" s="3" t="n"/>
       <c r="G146" s="3" t="n"/>
@@ -5771,20 +5851,16 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>Armie Rose Rey</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>Amaretto Sour</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C147" s="3" t="n">
-        <v>26540</v>
-      </c>
-      <c r="D147" s="3" t="n">
-        <v>151</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D147" s="3" t="n"/>
       <c r="E147" s="3" t="n"/>
       <c r="F147" s="3" t="n"/>
       <c r="G147" s="3" t="n"/>
@@ -5796,20 +5872,16 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>Rexan Gleem Gaid</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>Port Barton Sunset</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="C148" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="D148" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="D148" s="3" t="n"/>
       <c r="E148" s="3" t="n"/>
       <c r="F148" s="3" t="n"/>
       <c r="G148" s="3" t="n"/>
@@ -5821,20 +5893,16 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>Cherry Ann Lumactod</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>Pinacolada</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C149" s="3" t="n">
-        <v>7700</v>
-      </c>
-      <c r="D149" s="3" t="n">
-        <v>33</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D149" s="3" t="n"/>
       <c r="E149" s="3" t="n"/>
       <c r="F149" s="3" t="n"/>
       <c r="G149" s="3" t="n"/>
@@ -5846,20 +5914,16 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>Anna Mae Dela Fuente</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
+          <t>Sex On The Beach</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C150" s="3" t="n">
-        <v>20390</v>
-      </c>
-      <c r="D150" s="3" t="n">
-        <v>84</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D150" s="3" t="n"/>
       <c r="E150" s="3" t="n"/>
       <c r="F150" s="3" t="n"/>
       <c r="G150" s="3" t="n"/>
@@ -5868,123 +5932,45 @@
       <c r="J150" s="3" t="n"/>
       <c r="K150" s="3" t="n"/>
     </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>Joey Elijan</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="n">
-        <v>13890</v>
-      </c>
-      <c r="D151" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="E151" s="3" t="n"/>
-      <c r="F151" s="3" t="n"/>
-      <c r="G151" s="3" t="n"/>
-      <c r="H151" s="3" t="n"/>
-      <c r="I151" s="3" t="n"/>
-      <c r="J151" s="3" t="n"/>
-      <c r="K151" s="3" t="n"/>
-    </row>
+    <row r="151"/>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>Joraly Angeles</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="n">
-        <v>6500</v>
-      </c>
-      <c r="D152" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="E152" s="3" t="n"/>
-      <c r="F152" s="3" t="n"/>
-      <c r="G152" s="3" t="n"/>
-      <c r="H152" s="3" t="n"/>
-      <c r="I152" s="3" t="n"/>
-      <c r="J152" s="3" t="n"/>
-      <c r="K152" s="3" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>Kenneth John Mart Jusos</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="n">
-        <v>22310</v>
-      </c>
-      <c r="D153" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="E153" s="3" t="n"/>
-      <c r="F153" s="3" t="n"/>
-      <c r="G153" s="3" t="n"/>
-      <c r="H153" s="3" t="n"/>
-      <c r="I153" s="3" t="n"/>
-      <c r="J153" s="3" t="n"/>
-      <c r="K153" s="3" t="n"/>
-    </row>
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>THIS WEEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="153"/>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>Krisia Favila</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D154" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E154" s="3" t="n"/>
-      <c r="F154" s="3" t="n"/>
-      <c r="G154" s="3" t="n"/>
-      <c r="H154" s="3" t="n"/>
-      <c r="I154" s="3" t="n"/>
-      <c r="J154" s="3" t="n"/>
-      <c r="K154" s="3" t="n"/>
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Floating Net Sales</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Total Discount</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" s="2" t="n"/>
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="2" t="n"/>
+      <c r="H154" s="2" t="n"/>
+      <c r="I154" s="2" t="n"/>
+      <c r="J154" s="2" t="n"/>
+      <c r="K154" s="2" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>Daizer Raye Paglicawan</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="n">
-        <v>1020</v>
-      </c>
-      <c r="D155" s="3" t="n">
-        <v>4</v>
-      </c>
+      <c r="A155" s="3" t="n">
+        <v>17072</v>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" s="3" t="n"/>
+      <c r="D155" s="3" t="n"/>
       <c r="E155" s="3" t="n"/>
       <c r="F155" s="3" t="n"/>
       <c r="G155" s="3" t="n"/>
@@ -5993,13 +5979,2693 @@
       <c r="J155" s="3" t="n"/>
       <c r="K155" s="3" t="n"/>
     </row>
+    <row r="156"/>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n"/>
+      <c r="F157" s="2" t="n"/>
+      <c r="G157" s="2" t="n"/>
+      <c r="H157" s="2" t="n"/>
+      <c r="I157" s="2" t="n"/>
+      <c r="J157" s="2" t="n"/>
+      <c r="K157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n"/>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>cashier</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>17072</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="3" t="n"/>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
+      <c r="I158" s="3" t="n"/>
+      <c r="J158" s="3" t="n"/>
+      <c r="K158" s="3" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Krisia Favila</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="3" t="n"/>
+      <c r="G159" s="3" t="n"/>
+      <c r="H159" s="3" t="n"/>
+      <c r="I159" s="3" t="n"/>
+      <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Kenneth John Mart Jusos</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>1770</v>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
+      <c r="I160" s="3" t="n"/>
+      <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Anna Mae Dela Fuente</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>3150</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E161" s="3" t="n"/>
+      <c r="F161" s="3" t="n"/>
+      <c r="G161" s="3" t="n"/>
+      <c r="H161" s="3" t="n"/>
+      <c r="I161" s="3" t="n"/>
+      <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Joey Elijan</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>1540</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E162" s="3" t="n"/>
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
+      <c r="I162" s="3" t="n"/>
+      <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Armie Rose Rey</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>3050</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E163" s="3" t="n"/>
+      <c r="F163" s="3" t="n"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="3" t="n"/>
+      <c r="I163" s="3" t="n"/>
+      <c r="J163" s="3" t="n"/>
+      <c r="K163" s="3" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Daizer Raye Paglicawan</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E164" s="3" t="n"/>
+      <c r="F164" s="3" t="n"/>
+      <c r="G164" s="3" t="n"/>
+      <c r="H164" s="3" t="n"/>
+      <c r="I164" s="3" t="n"/>
+      <c r="J164" s="3" t="n"/>
+      <c r="K164" s="3" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>Joraly Angeles</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>4750</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E165" s="3" t="n"/>
+      <c r="F165" s="3" t="n"/>
+      <c r="G165" s="3" t="n"/>
+      <c r="H165" s="3" t="n"/>
+      <c r="I165" s="3" t="n"/>
+      <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="n"/>
+    </row>
+    <row r="166"/>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Item Sold</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n"/>
+      <c r="F167" s="2" t="n"/>
+      <c r="G167" s="2" t="n"/>
+      <c r="H167" s="2" t="n"/>
+      <c r="I167" s="2" t="n"/>
+      <c r="J167" s="2" t="n"/>
+      <c r="K167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>Sunset View - C1 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" s="3" t="n"/>
+      <c r="E168" s="3" t="n"/>
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="3" t="n"/>
+      <c r="H168" s="3" t="n"/>
+      <c r="I168" s="3" t="n"/>
+      <c r="J168" s="3" t="n"/>
+      <c r="K168" s="3" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Fruity Margarita</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D169" s="3" t="n"/>
+      <c r="E169" s="3" t="n"/>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="3" t="n"/>
+      <c r="K169" s="3" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>Port Barton Sunset</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D170" s="3" t="n"/>
+      <c r="E170" s="3" t="n"/>
+      <c r="F170" s="3" t="n"/>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="3" t="n"/>
+      <c r="I170" s="3" t="n"/>
+      <c r="J170" s="3" t="n"/>
+      <c r="K170" s="3" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Front Facade - T4 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" s="3" t="n"/>
+      <c r="E171" s="3" t="n"/>
+      <c r="F171" s="3" t="n"/>
+      <c r="G171" s="3" t="n"/>
+      <c r="H171" s="3" t="n"/>
+      <c r="I171" s="3" t="n"/>
+      <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Bottled Water</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D172" s="3" t="n"/>
+      <c r="E172" s="3" t="n"/>
+      <c r="F172" s="3" t="n"/>
+      <c r="G172" s="3" t="n"/>
+      <c r="H172" s="3" t="n"/>
+      <c r="I172" s="3" t="n"/>
+      <c r="J172" s="3" t="n"/>
+      <c r="K172" s="3" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Surf &amp; Turf Burger</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D173" s="3" t="n"/>
+      <c r="E173" s="3" t="n"/>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="3" t="n"/>
+      <c r="I173" s="3" t="n"/>
+      <c r="J173" s="3" t="n"/>
+      <c r="K173" s="3" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>San Mig Light</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D174" s="3" t="n"/>
+      <c r="E174" s="3" t="n"/>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="3" t="n"/>
+      <c r="H174" s="3" t="n"/>
+      <c r="I174" s="3" t="n"/>
+      <c r="J174" s="3" t="n"/>
+      <c r="K174" s="3" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>Tuna Crudo</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D175" s="3" t="n"/>
+      <c r="E175" s="3" t="n"/>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="3" t="n"/>
+      <c r="H175" s="3" t="n"/>
+      <c r="I175" s="3" t="n"/>
+      <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>Prawn Croquettes</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D176" s="3" t="n"/>
+      <c r="E176" s="3" t="n"/>
+      <c r="F176" s="3" t="n"/>
+      <c r="G176" s="3" t="n"/>
+      <c r="H176" s="3" t="n"/>
+      <c r="I176" s="3" t="n"/>
+      <c r="J176" s="3" t="n"/>
+      <c r="K176" s="3" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>Ginger-Basil-Cucumber Lemonade</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D177" s="3" t="n"/>
+      <c r="E177" s="3" t="n"/>
+      <c r="F177" s="3" t="n"/>
+      <c r="G177" s="3" t="n"/>
+      <c r="H177" s="3" t="n"/>
+      <c r="I177" s="3" t="n"/>
+      <c r="J177" s="3" t="n"/>
+      <c r="K177" s="3" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>BOTTLED WATER 500 ML</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D178" s="3" t="n"/>
+      <c r="E178" s="3" t="n"/>
+      <c r="F178" s="3" t="n"/>
+      <c r="G178" s="3" t="n"/>
+      <c r="H178" s="3" t="n"/>
+      <c r="I178" s="3" t="n"/>
+      <c r="J178" s="3" t="n"/>
+      <c r="K178" s="3" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>Tropicale</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D179" s="3" t="n"/>
+      <c r="E179" s="3" t="n"/>
+      <c r="F179" s="3" t="n"/>
+      <c r="G179" s="3" t="n"/>
+      <c r="H179" s="3" t="n"/>
+      <c r="I179" s="3" t="n"/>
+      <c r="J179" s="3" t="n"/>
+      <c r="K179" s="3" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>Pineapple</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="D180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="3" t="n"/>
+      <c r="G180" s="3" t="n"/>
+      <c r="H180" s="3" t="n"/>
+      <c r="I180" s="3" t="n"/>
+      <c r="J180" s="3" t="n"/>
+      <c r="K180" s="3" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>Cafe Latte</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D181" s="3" t="n"/>
+      <c r="E181" s="3" t="n"/>
+      <c r="F181" s="3" t="n"/>
+      <c r="G181" s="3" t="n"/>
+      <c r="H181" s="3" t="n"/>
+      <c r="I181" s="3" t="n"/>
+      <c r="J181" s="3" t="n"/>
+      <c r="K181" s="3" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>San Mig Pale Pilsen</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D182" s="3" t="n"/>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="3" t="n"/>
+      <c r="G182" s="3" t="n"/>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="n"/>
+      <c r="J182" s="3" t="n"/>
+      <c r="K182" s="3" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Margherita</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D183" s="3" t="n"/>
+      <c r="E183" s="3" t="n"/>
+      <c r="F183" s="3" t="n"/>
+      <c r="G183" s="3" t="n"/>
+      <c r="H183" s="3" t="n"/>
+      <c r="I183" s="3" t="n"/>
+      <c r="J183" s="3" t="n"/>
+      <c r="K183" s="3" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>Blue Ocean Mule</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D184" s="3" t="n"/>
+      <c r="E184" s="3" t="n"/>
+      <c r="F184" s="3" t="n"/>
+      <c r="G184" s="3" t="n"/>
+      <c r="H184" s="3" t="n"/>
+      <c r="I184" s="3" t="n"/>
+      <c r="J184" s="3" t="n"/>
+      <c r="K184" s="3" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>TANDUAY RUM</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="D185" s="3" t="n"/>
+      <c r="E185" s="3" t="n"/>
+      <c r="F185" s="3" t="n"/>
+      <c r="G185" s="3" t="n"/>
+      <c r="H185" s="3" t="n"/>
+      <c r="I185" s="3" t="n"/>
+      <c r="J185" s="3" t="n"/>
+      <c r="K185" s="3" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>COKE REGULAR</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="D186" s="3" t="n"/>
+      <c r="E186" s="3" t="n"/>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="3" t="n"/>
+      <c r="H186" s="3" t="n"/>
+      <c r="I186" s="3" t="n"/>
+      <c r="J186" s="3" t="n"/>
+      <c r="K186" s="3" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>Coke Zero</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D187" s="3" t="n"/>
+      <c r="E187" s="3" t="n"/>
+      <c r="F187" s="3" t="n"/>
+      <c r="G187" s="3" t="n"/>
+      <c r="H187" s="3" t="n"/>
+      <c r="I187" s="3" t="n"/>
+      <c r="J187" s="3" t="n"/>
+      <c r="K187" s="3" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>San Mig Apple</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D188" s="3" t="n"/>
+      <c r="E188" s="3" t="n"/>
+      <c r="F188" s="3" t="n"/>
+      <c r="G188" s="3" t="n"/>
+      <c r="H188" s="3" t="n"/>
+      <c r="I188" s="3" t="n"/>
+      <c r="J188" s="3" t="n"/>
+      <c r="K188" s="3" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Smoked Buffalo Wings</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D189" s="3" t="n"/>
+      <c r="E189" s="3" t="n"/>
+      <c r="F189" s="3" t="n"/>
+      <c r="G189" s="3" t="n"/>
+      <c r="H189" s="3" t="n"/>
+      <c r="I189" s="3" t="n"/>
+      <c r="J189" s="3" t="n"/>
+      <c r="K189" s="3" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>Pepperoni</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D190" s="3" t="n"/>
+      <c r="E190" s="3" t="n"/>
+      <c r="F190" s="3" t="n"/>
+      <c r="G190" s="3" t="n"/>
+      <c r="H190" s="3" t="n"/>
+      <c r="I190" s="3" t="n"/>
+      <c r="J190" s="3" t="n"/>
+      <c r="K190" s="3" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>TANQUERAY Per Shot</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="D191" s="3" t="n"/>
+      <c r="E191" s="3" t="n"/>
+      <c r="F191" s="3" t="n"/>
+      <c r="G191" s="3" t="n"/>
+      <c r="H191" s="3" t="n"/>
+      <c r="I191" s="3" t="n"/>
+      <c r="J191" s="3" t="n"/>
+      <c r="K191" s="3" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>Spiced Cinnamon Apple Spritz</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="D192" s="3" t="n"/>
+      <c r="E192" s="3" t="n"/>
+      <c r="F192" s="3" t="n"/>
+      <c r="G192" s="3" t="n"/>
+      <c r="H192" s="3" t="n"/>
+      <c r="I192" s="3" t="n"/>
+      <c r="J192" s="3" t="n"/>
+      <c r="K192" s="3" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>Amaretto Sour</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D193" s="3" t="n"/>
+      <c r="E193" s="3" t="n"/>
+      <c r="F193" s="3" t="n"/>
+      <c r="G193" s="3" t="n"/>
+      <c r="H193" s="3" t="n"/>
+      <c r="I193" s="3" t="n"/>
+      <c r="J193" s="3" t="n"/>
+      <c r="K193" s="3" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>Pinacolada</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D194" s="3" t="n"/>
+      <c r="E194" s="3" t="n"/>
+      <c r="F194" s="3" t="n"/>
+      <c r="G194" s="3" t="n"/>
+      <c r="H194" s="3" t="n"/>
+      <c r="I194" s="3" t="n"/>
+      <c r="J194" s="3" t="n"/>
+      <c r="K194" s="3" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>Sex On The Beach</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D195" s="3" t="n"/>
+      <c r="E195" s="3" t="n"/>
+      <c r="F195" s="3" t="n"/>
+      <c r="G195" s="3" t="n"/>
+      <c r="H195" s="3" t="n"/>
+      <c r="I195" s="3" t="n"/>
+      <c r="J195" s="3" t="n"/>
+      <c r="K195" s="3" t="n"/>
+    </row>
+    <row r="196"/>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>THIS MONTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="198"/>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Floating Net Sales</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Total Discount</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n"/>
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n"/>
+      <c r="F199" s="2" t="n"/>
+      <c r="G199" s="2" t="n"/>
+      <c r="H199" s="2" t="n"/>
+      <c r="I199" s="2" t="n"/>
+      <c r="J199" s="2" t="n"/>
+      <c r="K199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="n">
+        <v>207482</v>
+      </c>
+      <c r="B200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" s="3" t="n"/>
+      <c r="D200" s="3" t="n"/>
+      <c r="E200" s="3" t="n"/>
+      <c r="F200" s="3" t="n"/>
+      <c r="G200" s="3" t="n"/>
+      <c r="H200" s="3" t="n"/>
+      <c r="I200" s="3" t="n"/>
+      <c r="J200" s="3" t="n"/>
+      <c r="K200" s="3" t="n"/>
+    </row>
+    <row r="201"/>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n"/>
+      <c r="F202" s="2" t="n"/>
+      <c r="G202" s="2" t="n"/>
+      <c r="H202" s="2" t="n"/>
+      <c r="I202" s="2" t="n"/>
+      <c r="J202" s="2" t="n"/>
+      <c r="K202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n"/>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>cashier</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>207482</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" s="3" t="n"/>
+      <c r="F203" s="3" t="n"/>
+      <c r="G203" s="3" t="n"/>
+      <c r="H203" s="3" t="n"/>
+      <c r="I203" s="3" t="n"/>
+      <c r="J203" s="3" t="n"/>
+      <c r="K203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>Armie Rose Rey</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>26540</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="E204" s="3" t="n"/>
+      <c r="F204" s="3" t="n"/>
+      <c r="G204" s="3" t="n"/>
+      <c r="H204" s="3" t="n"/>
+      <c r="I204" s="3" t="n"/>
+      <c r="J204" s="3" t="n"/>
+      <c r="K204" s="3" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>Rexan Gleem Gaid</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E205" s="3" t="n"/>
+      <c r="F205" s="3" t="n"/>
+      <c r="G205" s="3" t="n"/>
+      <c r="H205" s="3" t="n"/>
+      <c r="I205" s="3" t="n"/>
+      <c r="J205" s="3" t="n"/>
+      <c r="K205" s="3" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>Cherry Ann Lumactod</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>7700</v>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E206" s="3" t="n"/>
+      <c r="F206" s="3" t="n"/>
+      <c r="G206" s="3" t="n"/>
+      <c r="H206" s="3" t="n"/>
+      <c r="I206" s="3" t="n"/>
+      <c r="J206" s="3" t="n"/>
+      <c r="K206" s="3" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>Anna Mae Dela Fuente</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>20390</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E207" s="3" t="n"/>
+      <c r="F207" s="3" t="n"/>
+      <c r="G207" s="3" t="n"/>
+      <c r="H207" s="3" t="n"/>
+      <c r="I207" s="3" t="n"/>
+      <c r="J207" s="3" t="n"/>
+      <c r="K207" s="3" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>Joey Elijan</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>13890</v>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="E208" s="3" t="n"/>
+      <c r="F208" s="3" t="n"/>
+      <c r="G208" s="3" t="n"/>
+      <c r="H208" s="3" t="n"/>
+      <c r="I208" s="3" t="n"/>
+      <c r="J208" s="3" t="n"/>
+      <c r="K208" s="3" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>Joraly Angeles</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>6500</v>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E209" s="3" t="n"/>
+      <c r="F209" s="3" t="n"/>
+      <c r="G209" s="3" t="n"/>
+      <c r="H209" s="3" t="n"/>
+      <c r="I209" s="3" t="n"/>
+      <c r="J209" s="3" t="n"/>
+      <c r="K209" s="3" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>Kenneth John Mart Jusos</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>22310</v>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="E210" s="3" t="n"/>
+      <c r="F210" s="3" t="n"/>
+      <c r="G210" s="3" t="n"/>
+      <c r="H210" s="3" t="n"/>
+      <c r="I210" s="3" t="n"/>
+      <c r="J210" s="3" t="n"/>
+      <c r="K210" s="3" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>Krisia Favila</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E211" s="3" t="n"/>
+      <c r="F211" s="3" t="n"/>
+      <c r="G211" s="3" t="n"/>
+      <c r="H211" s="3" t="n"/>
+      <c r="I211" s="3" t="n"/>
+      <c r="J211" s="3" t="n"/>
+      <c r="K211" s="3" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>Daizer Raye Paglicawan</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>waiter</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E212" s="3" t="n"/>
+      <c r="F212" s="3" t="n"/>
+      <c r="G212" s="3" t="n"/>
+      <c r="H212" s="3" t="n"/>
+      <c r="I212" s="3" t="n"/>
+      <c r="J212" s="3" t="n"/>
+      <c r="K212" s="3" t="n"/>
+    </row>
+    <row r="213"/>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Item Sold</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="n"/>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="2" t="n"/>
+      <c r="G214" s="2" t="n"/>
+      <c r="H214" s="2" t="n"/>
+      <c r="I214" s="2" t="n"/>
+      <c r="J214" s="2" t="n"/>
+      <c r="K214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D215" s="3" t="n"/>
+      <c r="E215" s="3" t="n"/>
+      <c r="F215" s="3" t="n"/>
+      <c r="G215" s="3" t="n"/>
+      <c r="H215" s="3" t="n"/>
+      <c r="I215" s="3" t="n"/>
+      <c r="J215" s="3" t="n"/>
+      <c r="K215" s="3" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>Calamares</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D216" s="3" t="n"/>
+      <c r="E216" s="3" t="n"/>
+      <c r="F216" s="3" t="n"/>
+      <c r="G216" s="3" t="n"/>
+      <c r="H216" s="3" t="n"/>
+      <c r="I216" s="3" t="n"/>
+      <c r="J216" s="3" t="n"/>
+      <c r="K216" s="3" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D217" s="3" t="n"/>
+      <c r="E217" s="3" t="n"/>
+      <c r="F217" s="3" t="n"/>
+      <c r="G217" s="3" t="n"/>
+      <c r="H217" s="3" t="n"/>
+      <c r="I217" s="3" t="n"/>
+      <c r="J217" s="3" t="n"/>
+      <c r="K217" s="3" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C218" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D218" s="3" t="n"/>
+      <c r="E218" s="3" t="n"/>
+      <c r="F218" s="3" t="n"/>
+      <c r="G218" s="3" t="n"/>
+      <c r="H218" s="3" t="n"/>
+      <c r="I218" s="3" t="n"/>
+      <c r="J218" s="3" t="n"/>
+      <c r="K218" s="3" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>KAYAKING</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D219" s="3" t="n"/>
+      <c r="E219" s="3" t="n"/>
+      <c r="F219" s="3" t="n"/>
+      <c r="G219" s="3" t="n"/>
+      <c r="H219" s="3" t="n"/>
+      <c r="I219" s="3" t="n"/>
+      <c r="J219" s="3" t="n"/>
+      <c r="K219" s="3" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>Smoked Buffalo Wings</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C220" s="3" t="n">
+        <v>7600</v>
+      </c>
+      <c r="D220" s="3" t="n"/>
+      <c r="E220" s="3" t="n"/>
+      <c r="F220" s="3" t="n"/>
+      <c r="G220" s="3" t="n"/>
+      <c r="H220" s="3" t="n"/>
+      <c r="I220" s="3" t="n"/>
+      <c r="J220" s="3" t="n"/>
+      <c r="K220" s="3" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>Tropicale</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>3900</v>
+      </c>
+      <c r="D221" s="3" t="n"/>
+      <c r="E221" s="3" t="n"/>
+      <c r="F221" s="3" t="n"/>
+      <c r="G221" s="3" t="n"/>
+      <c r="H221" s="3" t="n"/>
+      <c r="I221" s="3" t="n"/>
+      <c r="J221" s="3" t="n"/>
+      <c r="K221" s="3" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>Sunset View - C1 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" s="3" t="n"/>
+      <c r="E222" s="3" t="n"/>
+      <c r="F222" s="3" t="n"/>
+      <c r="G222" s="3" t="n"/>
+      <c r="H222" s="3" t="n"/>
+      <c r="I222" s="3" t="n"/>
+      <c r="J222" s="3" t="n"/>
+      <c r="K222" s="3" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>Front Facade - T18 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" s="3" t="n"/>
+      <c r="E223" s="3" t="n"/>
+      <c r="F223" s="3" t="n"/>
+      <c r="G223" s="3" t="n"/>
+      <c r="H223" s="3" t="n"/>
+      <c r="I223" s="3" t="n"/>
+      <c r="J223" s="3" t="n"/>
+      <c r="K223" s="3" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>Front Facade - T19 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" s="3" t="n"/>
+      <c r="E224" s="3" t="n"/>
+      <c r="F224" s="3" t="n"/>
+      <c r="G224" s="3" t="n"/>
+      <c r="H224" s="3" t="n"/>
+      <c r="I224" s="3" t="n"/>
+      <c r="J224" s="3" t="n"/>
+      <c r="K224" s="3" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>Sunset View - C2 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" s="3" t="n"/>
+      <c r="E225" s="3" t="n"/>
+      <c r="F225" s="3" t="n"/>
+      <c r="G225" s="3" t="n"/>
+      <c r="H225" s="3" t="n"/>
+      <c r="I225" s="3" t="n"/>
+      <c r="J225" s="3" t="n"/>
+      <c r="K225" s="3" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>Sunset View - C3 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" s="3" t="n"/>
+      <c r="E226" s="3" t="n"/>
+      <c r="F226" s="3" t="n"/>
+      <c r="G226" s="3" t="n"/>
+      <c r="H226" s="3" t="n"/>
+      <c r="I226" s="3" t="n"/>
+      <c r="J226" s="3" t="n"/>
+      <c r="K226" s="3" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>Pepperoni</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>11200</v>
+      </c>
+      <c r="D227" s="3" t="n"/>
+      <c r="E227" s="3" t="n"/>
+      <c r="F227" s="3" t="n"/>
+      <c r="G227" s="3" t="n"/>
+      <c r="H227" s="3" t="n"/>
+      <c r="I227" s="3" t="n"/>
+      <c r="J227" s="3" t="n"/>
+      <c r="K227" s="3" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>Wahoo Ceviche</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D228" s="3" t="n"/>
+      <c r="E228" s="3" t="n"/>
+      <c r="F228" s="3" t="n"/>
+      <c r="G228" s="3" t="n"/>
+      <c r="H228" s="3" t="n"/>
+      <c r="I228" s="3" t="n"/>
+      <c r="J228" s="3" t="n"/>
+      <c r="K228" s="3" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>San Mig Light</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>4950</v>
+      </c>
+      <c r="D229" s="3" t="n"/>
+      <c r="E229" s="3" t="n"/>
+      <c r="F229" s="3" t="n"/>
+      <c r="G229" s="3" t="n"/>
+      <c r="H229" s="3" t="n"/>
+      <c r="I229" s="3" t="n"/>
+      <c r="J229" s="3" t="n"/>
+      <c r="K229" s="3" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>Sex On The Beach</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D230" s="3" t="n"/>
+      <c r="E230" s="3" t="n"/>
+      <c r="F230" s="3" t="n"/>
+      <c r="G230" s="3" t="n"/>
+      <c r="H230" s="3" t="n"/>
+      <c r="I230" s="3" t="n"/>
+      <c r="J230" s="3" t="n"/>
+      <c r="K230" s="3" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>Fruity Margarita</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>5700</v>
+      </c>
+      <c r="D231" s="3" t="n"/>
+      <c r="E231" s="3" t="n"/>
+      <c r="F231" s="3" t="n"/>
+      <c r="G231" s="3" t="n"/>
+      <c r="H231" s="3" t="n"/>
+      <c r="I231" s="3" t="n"/>
+      <c r="J231" s="3" t="n"/>
+      <c r="K231" s="3" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>Tuna Crudo</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C232" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D232" s="3" t="n"/>
+      <c r="E232" s="3" t="n"/>
+      <c r="F232" s="3" t="n"/>
+      <c r="G232" s="3" t="n"/>
+      <c r="H232" s="3" t="n"/>
+      <c r="I232" s="3" t="n"/>
+      <c r="J232" s="3" t="n"/>
+      <c r="K232" s="3" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>Caipiranha</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="D233" s="3" t="n"/>
+      <c r="E233" s="3" t="n"/>
+      <c r="F233" s="3" t="n"/>
+      <c r="G233" s="3" t="n"/>
+      <c r="H233" s="3" t="n"/>
+      <c r="I233" s="3" t="n"/>
+      <c r="J233" s="3" t="n"/>
+      <c r="K233" s="3" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>Cosmopolitan</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D234" s="3" t="n"/>
+      <c r="E234" s="3" t="n"/>
+      <c r="F234" s="3" t="n"/>
+      <c r="G234" s="3" t="n"/>
+      <c r="H234" s="3" t="n"/>
+      <c r="I234" s="3" t="n"/>
+      <c r="J234" s="3" t="n"/>
+      <c r="K234" s="3" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>Ragu Alla Bolognese With Parmesan Espuma</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D235" s="3" t="n"/>
+      <c r="E235" s="3" t="n"/>
+      <c r="F235" s="3" t="n"/>
+      <c r="G235" s="3" t="n"/>
+      <c r="H235" s="3" t="n"/>
+      <c r="I235" s="3" t="n"/>
+      <c r="J235" s="3" t="n"/>
+      <c r="K235" s="3" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>Ginger-Basil-Cucumber Lemonade</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D236" s="3" t="n"/>
+      <c r="E236" s="3" t="n"/>
+      <c r="F236" s="3" t="n"/>
+      <c r="G236" s="3" t="n"/>
+      <c r="H236" s="3" t="n"/>
+      <c r="I236" s="3" t="n"/>
+      <c r="J236" s="3" t="n"/>
+      <c r="K236" s="3" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>San Mig Pale Pilsen</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D237" s="3" t="n"/>
+      <c r="E237" s="3" t="n"/>
+      <c r="F237" s="3" t="n"/>
+      <c r="G237" s="3" t="n"/>
+      <c r="H237" s="3" t="n"/>
+      <c r="I237" s="3" t="n"/>
+      <c r="J237" s="3" t="n"/>
+      <c r="K237" s="3" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>Bottled Water</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C238" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D238" s="3" t="n"/>
+      <c r="E238" s="3" t="n"/>
+      <c r="F238" s="3" t="n"/>
+      <c r="G238" s="3" t="n"/>
+      <c r="H238" s="3" t="n"/>
+      <c r="I238" s="3" t="n"/>
+      <c r="J238" s="3" t="n"/>
+      <c r="K238" s="3" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>Coke Zero</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>840</v>
+      </c>
+      <c r="D239" s="3" t="n"/>
+      <c r="E239" s="3" t="n"/>
+      <c r="F239" s="3" t="n"/>
+      <c r="G239" s="3" t="n"/>
+      <c r="H239" s="3" t="n"/>
+      <c r="I239" s="3" t="n"/>
+      <c r="J239" s="3" t="n"/>
+      <c r="K239" s="3" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>Cafe Latte</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D240" s="3" t="n"/>
+      <c r="E240" s="3" t="n"/>
+      <c r="F240" s="3" t="n"/>
+      <c r="G240" s="3" t="n"/>
+      <c r="H240" s="3" t="n"/>
+      <c r="I240" s="3" t="n"/>
+      <c r="J240" s="3" t="n"/>
+      <c r="K240" s="3" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>Carbonara Oceanica</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D241" s="3" t="n"/>
+      <c r="E241" s="3" t="n"/>
+      <c r="F241" s="3" t="n"/>
+      <c r="G241" s="3" t="n"/>
+      <c r="H241" s="3" t="n"/>
+      <c r="I241" s="3" t="n"/>
+      <c r="J241" s="3" t="n"/>
+      <c r="K241" s="3" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>Sprite</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C242" s="3" t="n">
+        <v>1080</v>
+      </c>
+      <c r="D242" s="3" t="n"/>
+      <c r="E242" s="3" t="n"/>
+      <c r="F242" s="3" t="n"/>
+      <c r="G242" s="3" t="n"/>
+      <c r="H242" s="3" t="n"/>
+      <c r="I242" s="3" t="n"/>
+      <c r="J242" s="3" t="n"/>
+      <c r="K242" s="3" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>Margherita</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D243" s="3" t="n"/>
+      <c r="E243" s="3" t="n"/>
+      <c r="F243" s="3" t="n"/>
+      <c r="G243" s="3" t="n"/>
+      <c r="H243" s="3" t="n"/>
+      <c r="I243" s="3" t="n"/>
+      <c r="J243" s="3" t="n"/>
+      <c r="K243" s="3" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>San Mig Pure Malt</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C244" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D244" s="3" t="n"/>
+      <c r="E244" s="3" t="n"/>
+      <c r="F244" s="3" t="n"/>
+      <c r="G244" s="3" t="n"/>
+      <c r="H244" s="3" t="n"/>
+      <c r="I244" s="3" t="n"/>
+      <c r="J244" s="3" t="n"/>
+      <c r="K244" s="3" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>MAI TAI WD</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="C245" s="3" t="n">
+        <v>12250</v>
+      </c>
+      <c r="D245" s="3" t="n"/>
+      <c r="E245" s="3" t="n"/>
+      <c r="F245" s="3" t="n"/>
+      <c r="G245" s="3" t="n"/>
+      <c r="H245" s="3" t="n"/>
+      <c r="I245" s="3" t="n"/>
+      <c r="J245" s="3" t="n"/>
+      <c r="K245" s="3" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="C246" s="3" t="n">
+        <v>55500</v>
+      </c>
+      <c r="D246" s="3" t="n"/>
+      <c r="E246" s="3" t="n"/>
+      <c r="F246" s="3" t="n"/>
+      <c r="G246" s="3" t="n"/>
+      <c r="H246" s="3" t="n"/>
+      <c r="I246" s="3" t="n"/>
+      <c r="J246" s="3" t="n"/>
+      <c r="K246" s="3" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>Jacuzzi Couch - C4 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" s="3" t="n"/>
+      <c r="E247" s="3" t="n"/>
+      <c r="F247" s="3" t="n"/>
+      <c r="G247" s="3" t="n"/>
+      <c r="H247" s="3" t="n"/>
+      <c r="I247" s="3" t="n"/>
+      <c r="J247" s="3" t="n"/>
+      <c r="K247" s="3" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>Jacuzzi Couch - C7 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" s="3" t="n"/>
+      <c r="E248" s="3" t="n"/>
+      <c r="F248" s="3" t="n"/>
+      <c r="G248" s="3" t="n"/>
+      <c r="H248" s="3" t="n"/>
+      <c r="I248" s="3" t="n"/>
+      <c r="J248" s="3" t="n"/>
+      <c r="K248" s="3" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>Prawn Croquettes</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C249" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D249" s="3" t="n"/>
+      <c r="E249" s="3" t="n"/>
+      <c r="F249" s="3" t="n"/>
+      <c r="G249" s="3" t="n"/>
+      <c r="H249" s="3" t="n"/>
+      <c r="I249" s="3" t="n"/>
+      <c r="J249" s="3" t="n"/>
+      <c r="K249" s="3" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>Marina Verde Lasagna</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C250" s="3" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D250" s="3" t="n"/>
+      <c r="E250" s="3" t="n"/>
+      <c r="F250" s="3" t="n"/>
+      <c r="G250" s="3" t="n"/>
+      <c r="H250" s="3" t="n"/>
+      <c r="I250" s="3" t="n"/>
+      <c r="J250" s="3" t="n"/>
+      <c r="K250" s="3" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>Cafe Mocha</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C251" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D251" s="3" t="n"/>
+      <c r="E251" s="3" t="n"/>
+      <c r="F251" s="3" t="n"/>
+      <c r="G251" s="3" t="n"/>
+      <c r="H251" s="3" t="n"/>
+      <c r="I251" s="3" t="n"/>
+      <c r="J251" s="3" t="n"/>
+      <c r="K251" s="3" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>Front Facade - T1 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" s="3" t="n"/>
+      <c r="E252" s="3" t="n"/>
+      <c r="F252" s="3" t="n"/>
+      <c r="G252" s="3" t="n"/>
+      <c r="H252" s="3" t="n"/>
+      <c r="I252" s="3" t="n"/>
+      <c r="J252" s="3" t="n"/>
+      <c r="K252" s="3" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>Daiquiri</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C253" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D253" s="3" t="n"/>
+      <c r="E253" s="3" t="n"/>
+      <c r="F253" s="3" t="n"/>
+      <c r="G253" s="3" t="n"/>
+      <c r="H253" s="3" t="n"/>
+      <c r="I253" s="3" t="n"/>
+      <c r="J253" s="3" t="n"/>
+      <c r="K253" s="3" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>Fruity Daiqueri</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C254" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D254" s="3" t="n"/>
+      <c r="E254" s="3" t="n"/>
+      <c r="F254" s="3" t="n"/>
+      <c r="G254" s="3" t="n"/>
+      <c r="H254" s="3" t="n"/>
+      <c r="I254" s="3" t="n"/>
+      <c r="J254" s="3" t="n"/>
+      <c r="K254" s="3" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>JOSE CUERVO GOLD 1Lt.</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" s="3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D255" s="3" t="n"/>
+      <c r="E255" s="3" t="n"/>
+      <c r="F255" s="3" t="n"/>
+      <c r="G255" s="3" t="n"/>
+      <c r="H255" s="3" t="n"/>
+      <c r="I255" s="3" t="n"/>
+      <c r="J255" s="3" t="n"/>
+      <c r="K255" s="3" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>San Mig Apple</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C256" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D256" s="3" t="n"/>
+      <c r="E256" s="3" t="n"/>
+      <c r="F256" s="3" t="n"/>
+      <c r="G256" s="3" t="n"/>
+      <c r="H256" s="3" t="n"/>
+      <c r="I256" s="3" t="n"/>
+      <c r="J256" s="3" t="n"/>
+      <c r="K256" s="3" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>Angus Ribeye</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D257" s="3" t="n"/>
+      <c r="E257" s="3" t="n"/>
+      <c r="F257" s="3" t="n"/>
+      <c r="G257" s="3" t="n"/>
+      <c r="H257" s="3" t="n"/>
+      <c r="I257" s="3" t="n"/>
+      <c r="J257" s="3" t="n"/>
+      <c r="K257" s="3" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>Espresso</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C258" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D258" s="3" t="n"/>
+      <c r="E258" s="3" t="n"/>
+      <c r="F258" s="3" t="n"/>
+      <c r="G258" s="3" t="n"/>
+      <c r="H258" s="3" t="n"/>
+      <c r="I258" s="3" t="n"/>
+      <c r="J258" s="3" t="n"/>
+      <c r="K258" s="3" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>JACK DANIELS Per Shot</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="D259" s="3" t="n"/>
+      <c r="E259" s="3" t="n"/>
+      <c r="F259" s="3" t="n"/>
+      <c r="G259" s="3" t="n"/>
+      <c r="H259" s="3" t="n"/>
+      <c r="I259" s="3" t="n"/>
+      <c r="J259" s="3" t="n"/>
+      <c r="K259" s="3" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>Mango Lemonade</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D260" s="3" t="n"/>
+      <c r="E260" s="3" t="n"/>
+      <c r="F260" s="3" t="n"/>
+      <c r="G260" s="3" t="n"/>
+      <c r="H260" s="3" t="n"/>
+      <c r="I260" s="3" t="n"/>
+      <c r="J260" s="3" t="n"/>
+      <c r="K260" s="3" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>MAI TAI N/A</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D261" s="3" t="n"/>
+      <c r="E261" s="3" t="n"/>
+      <c r="F261" s="3" t="n"/>
+      <c r="G261" s="3" t="n"/>
+      <c r="H261" s="3" t="n"/>
+      <c r="I261" s="3" t="n"/>
+      <c r="J261" s="3" t="n"/>
+      <c r="K261" s="3" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>Blue Ocean Mule</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>4950</v>
+      </c>
+      <c r="D262" s="3" t="n"/>
+      <c r="E262" s="3" t="n"/>
+      <c r="F262" s="3" t="n"/>
+      <c r="G262" s="3" t="n"/>
+      <c r="H262" s="3" t="n"/>
+      <c r="I262" s="3" t="n"/>
+      <c r="J262" s="3" t="n"/>
+      <c r="K262" s="3" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>Pinacolada</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D263" s="3" t="n"/>
+      <c r="E263" s="3" t="n"/>
+      <c r="F263" s="3" t="n"/>
+      <c r="G263" s="3" t="n"/>
+      <c r="H263" s="3" t="n"/>
+      <c r="I263" s="3" t="n"/>
+      <c r="J263" s="3" t="n"/>
+      <c r="K263" s="3" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>Coke Regular</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="D264" s="3" t="n"/>
+      <c r="E264" s="3" t="n"/>
+      <c r="F264" s="3" t="n"/>
+      <c r="G264" s="3" t="n"/>
+      <c r="H264" s="3" t="n"/>
+      <c r="I264" s="3" t="n"/>
+      <c r="J264" s="3" t="n"/>
+      <c r="K264" s="3" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>Day Access</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D265" s="3" t="n"/>
+      <c r="E265" s="3" t="n"/>
+      <c r="F265" s="3" t="n"/>
+      <c r="G265" s="3" t="n"/>
+      <c r="H265" s="3" t="n"/>
+      <c r="I265" s="3" t="n"/>
+      <c r="J265" s="3" t="n"/>
+      <c r="K265" s="3" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>Amaretto Sour</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D266" s="3" t="n"/>
+      <c r="E266" s="3" t="n"/>
+      <c r="F266" s="3" t="n"/>
+      <c r="G266" s="3" t="n"/>
+      <c r="H266" s="3" t="n"/>
+      <c r="I266" s="3" t="n"/>
+      <c r="J266" s="3" t="n"/>
+      <c r="K266" s="3" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>Surf &amp; Turf Burger</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>5360</v>
+      </c>
+      <c r="D267" s="3" t="n"/>
+      <c r="E267" s="3" t="n"/>
+      <c r="F267" s="3" t="n"/>
+      <c r="G267" s="3" t="n"/>
+      <c r="H267" s="3" t="n"/>
+      <c r="I267" s="3" t="n"/>
+      <c r="J267" s="3" t="n"/>
+      <c r="K267" s="3" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Towel </t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D268" s="3" t="n"/>
+      <c r="E268" s="3" t="n"/>
+      <c r="F268" s="3" t="n"/>
+      <c r="G268" s="3" t="n"/>
+      <c r="H268" s="3" t="n"/>
+      <c r="I268" s="3" t="n"/>
+      <c r="J268" s="3" t="n"/>
+      <c r="K268" s="3" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="D269" s="3" t="n"/>
+      <c r="E269" s="3" t="n"/>
+      <c r="F269" s="3" t="n"/>
+      <c r="G269" s="3" t="n"/>
+      <c r="H269" s="3" t="n"/>
+      <c r="I269" s="3" t="n"/>
+      <c r="J269" s="3" t="n"/>
+      <c r="K269" s="3" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>Pineapple</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D270" s="3" t="n"/>
+      <c r="E270" s="3" t="n"/>
+      <c r="F270" s="3" t="n"/>
+      <c r="G270" s="3" t="n"/>
+      <c r="H270" s="3" t="n"/>
+      <c r="I270" s="3" t="n"/>
+      <c r="J270" s="3" t="n"/>
+      <c r="K270" s="3" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>MATUA SAUV. BLANC HOUSE WINE</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D271" s="3" t="n"/>
+      <c r="E271" s="3" t="n"/>
+      <c r="F271" s="3" t="n"/>
+      <c r="G271" s="3" t="n"/>
+      <c r="H271" s="3" t="n"/>
+      <c r="I271" s="3" t="n"/>
+      <c r="J271" s="3" t="n"/>
+      <c r="K271" s="3" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>Port Barton Sunset</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D272" s="3" t="n"/>
+      <c r="E272" s="3" t="n"/>
+      <c r="F272" s="3" t="n"/>
+      <c r="G272" s="3" t="n"/>
+      <c r="H272" s="3" t="n"/>
+      <c r="I272" s="3" t="n"/>
+      <c r="J272" s="3" t="n"/>
+      <c r="K272" s="3" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>Margarita</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D273" s="3" t="n"/>
+      <c r="E273" s="3" t="n"/>
+      <c r="F273" s="3" t="n"/>
+      <c r="G273" s="3" t="n"/>
+      <c r="H273" s="3" t="n"/>
+      <c r="I273" s="3" t="n"/>
+      <c r="J273" s="3" t="n"/>
+      <c r="K273" s="3" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>Spiced Cinnamon Apple Spritz</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C274" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D274" s="3" t="n"/>
+      <c r="E274" s="3" t="n"/>
+      <c r="F274" s="3" t="n"/>
+      <c r="G274" s="3" t="n"/>
+      <c r="H274" s="3" t="n"/>
+      <c r="I274" s="3" t="n"/>
+      <c r="J274" s="3" t="n"/>
+      <c r="K274" s="3" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>Coconut Mousse</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C275" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D275" s="3" t="n"/>
+      <c r="E275" s="3" t="n"/>
+      <c r="F275" s="3" t="n"/>
+      <c r="G275" s="3" t="n"/>
+      <c r="H275" s="3" t="n"/>
+      <c r="I275" s="3" t="n"/>
+      <c r="J275" s="3" t="n"/>
+      <c r="K275" s="3" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>Sambuka</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D276" s="3" t="n"/>
+      <c r="E276" s="3" t="n"/>
+      <c r="F276" s="3" t="n"/>
+      <c r="G276" s="3" t="n"/>
+      <c r="H276" s="3" t="n"/>
+      <c r="I276" s="3" t="n"/>
+      <c r="J276" s="3" t="n"/>
+      <c r="K276" s="3" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>SHOT JOSE CUERVO GOLD</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D277" s="3" t="n"/>
+      <c r="E277" s="3" t="n"/>
+      <c r="F277" s="3" t="n"/>
+      <c r="G277" s="3" t="n"/>
+      <c r="H277" s="3" t="n"/>
+      <c r="I277" s="3" t="n"/>
+      <c r="J277" s="3" t="n"/>
+      <c r="K277" s="3" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>Cappuccino</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C278" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="D278" s="3" t="n"/>
+      <c r="E278" s="3" t="n"/>
+      <c r="F278" s="3" t="n"/>
+      <c r="G278" s="3" t="n"/>
+      <c r="H278" s="3" t="n"/>
+      <c r="I278" s="3" t="n"/>
+      <c r="J278" s="3" t="n"/>
+      <c r="K278" s="3" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>Estrella Galicia</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="D279" s="3" t="n"/>
+      <c r="E279" s="3" t="n"/>
+      <c r="F279" s="3" t="n"/>
+      <c r="G279" s="3" t="n"/>
+      <c r="H279" s="3" t="n"/>
+      <c r="I279" s="3" t="n"/>
+      <c r="J279" s="3" t="n"/>
+      <c r="K279" s="3" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>HAWAIIAN</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="D280" s="3" t="n"/>
+      <c r="E280" s="3" t="n"/>
+      <c r="F280" s="3" t="n"/>
+      <c r="G280" s="3" t="n"/>
+      <c r="H280" s="3" t="n"/>
+      <c r="I280" s="3" t="n"/>
+      <c r="J280" s="3" t="n"/>
+      <c r="K280" s="3" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>Front Facade - T4 - Main Deck</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C281" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" s="3" t="n"/>
+      <c r="E281" s="3" t="n"/>
+      <c r="F281" s="3" t="n"/>
+      <c r="G281" s="3" t="n"/>
+      <c r="H281" s="3" t="n"/>
+      <c r="I281" s="3" t="n"/>
+      <c r="J281" s="3" t="n"/>
+      <c r="K281" s="3" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>BOTTLED WATER 500 ML</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D282" s="3" t="n"/>
+      <c r="E282" s="3" t="n"/>
+      <c r="F282" s="3" t="n"/>
+      <c r="G282" s="3" t="n"/>
+      <c r="H282" s="3" t="n"/>
+      <c r="I282" s="3" t="n"/>
+      <c r="J282" s="3" t="n"/>
+      <c r="K282" s="3" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>TANDUAY RUM</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C283" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="D283" s="3" t="n"/>
+      <c r="E283" s="3" t="n"/>
+      <c r="F283" s="3" t="n"/>
+      <c r="G283" s="3" t="n"/>
+      <c r="H283" s="3" t="n"/>
+      <c r="I283" s="3" t="n"/>
+      <c r="J283" s="3" t="n"/>
+      <c r="K283" s="3" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>COKE REGULAR</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C284" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="D284" s="3" t="n"/>
+      <c r="E284" s="3" t="n"/>
+      <c r="F284" s="3" t="n"/>
+      <c r="G284" s="3" t="n"/>
+      <c r="H284" s="3" t="n"/>
+      <c r="I284" s="3" t="n"/>
+      <c r="J284" s="3" t="n"/>
+      <c r="K284" s="3" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>TANQUERAY Per Shot</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C285" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="D285" s="3" t="n"/>
+      <c r="E285" s="3" t="n"/>
+      <c r="F285" s="3" t="n"/>
+      <c r="G285" s="3" t="n"/>
+      <c r="H285" s="3" t="n"/>
+      <c r="I285" s="3" t="n"/>
+      <c r="J285" s="3" t="n"/>
+      <c r="K285" s="3" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A114:K114"/>
     <mergeCell ref="A105:K105"/>
-    <mergeCell ref="A140:K140"/>
-    <mergeCell ref="A112:K112"/>
-    <mergeCell ref="A125:K125"/>
+    <mergeCell ref="A152:K152"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A197:K197"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
